--- a/Arquivos/nao_atualizaveis/Ativo_IMES/DISCAGEM_IMES.xlsx
+++ b/Arquivos/nao_atualizaveis/Ativo_IMES/DISCAGEM_IMES.xlsx
@@ -5,22 +5,25 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Ativo_MES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Ativo_IMES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{468ECC7D-2A8F-4DE6-9368-37DAF76AF86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CF91A7-9AD2-49A2-A28F-A831926327D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{123B1522-D3FF-4DAC-9F1A-AEADB0465F69}"/>
   </bookViews>
   <sheets>
     <sheet name="chamadas_30-09-2026_134043" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'chamadas_30-09-2026_134043'!$A$1:$S$166</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="88">
   <si>
     <t>DATA</t>
   </si>
@@ -152,6 +155,138 @@
   </si>
   <si>
     <t>(32) 98497-7635</t>
+  </si>
+  <si>
+    <t>(11) 99577-1020</t>
+  </si>
+  <si>
+    <t>(22) 98163-2481</t>
+  </si>
+  <si>
+    <t>97282-2205</t>
+  </si>
+  <si>
+    <t>99427-0849</t>
+  </si>
+  <si>
+    <t>98105-0665</t>
+  </si>
+  <si>
+    <t>99747-1975</t>
+  </si>
+  <si>
+    <t>Recado</t>
+  </si>
+  <si>
+    <t>98017-8014</t>
+  </si>
+  <si>
+    <t>99368-7600</t>
+  </si>
+  <si>
+    <t>97173-3456</t>
+  </si>
+  <si>
+    <t>98801-0202</t>
+  </si>
+  <si>
+    <t>99816-4883</t>
+  </si>
+  <si>
+    <t>99981-3239</t>
+  </si>
+  <si>
+    <t>97220-0133</t>
+  </si>
+  <si>
+    <t>99465-6451</t>
+  </si>
+  <si>
+    <t>(22) 99251-2761</t>
+  </si>
+  <si>
+    <t>Fora de Area / Cx de Mensagens</t>
+  </si>
+  <si>
+    <t>97096-9352</t>
+  </si>
+  <si>
+    <t>99904-2857</t>
+  </si>
+  <si>
+    <t>99144-9724</t>
+  </si>
+  <si>
+    <t>99528-6333</t>
+  </si>
+  <si>
+    <t>99910-1976</t>
+  </si>
+  <si>
+    <t>2588-7353</t>
+  </si>
+  <si>
+    <t>2588-7466</t>
+  </si>
+  <si>
+    <t>(47) 99212-2812</t>
+  </si>
+  <si>
+    <t>(22) 99790-4539</t>
+  </si>
+  <si>
+    <t>97133-0457</t>
+  </si>
+  <si>
+    <t>98171-2143</t>
+  </si>
+  <si>
+    <t>99774-2251</t>
+  </si>
+  <si>
+    <t>(22) 99999-5946</t>
+  </si>
+  <si>
+    <t>98801-0429</t>
+  </si>
+  <si>
+    <t>99888-1953</t>
+  </si>
+  <si>
+    <t>98153-3282</t>
+  </si>
+  <si>
+    <t>(11) 97208-7606</t>
+  </si>
+  <si>
+    <t>97956-9770</t>
+  </si>
+  <si>
+    <t>97045-6846</t>
+  </si>
+  <si>
+    <t>97641-0956</t>
+  </si>
+  <si>
+    <t>99227-6215</t>
+  </si>
+  <si>
+    <t>99100-4284</t>
+  </si>
+  <si>
+    <t>99100-1072</t>
+  </si>
+  <si>
+    <t>96878-6403</t>
+  </si>
+  <si>
+    <t>NAO INTERESSADO</t>
+  </si>
+  <si>
+    <t>Confirmado</t>
+  </si>
+  <si>
+    <t>Troca de Representante</t>
   </si>
 </sst>
 </file>
@@ -995,28 +1130,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{100F3FCB-6525-4D20-BE0A-5478D5F6F3FE}">
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S166"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -1147,6 +1282,9 @@
       <c r="K3" t="s">
         <v>24</v>
       </c>
+      <c r="L3" t="s">
+        <v>86</v>
+      </c>
       <c r="N3" t="s">
         <v>25</v>
       </c>
@@ -1706,6 +1844,6378 @@
       </c>
       <c r="S16" s="3">
         <v>8.1018518518518516E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46295.395856481482</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>2786542433</v>
+      </c>
+      <c r="G17" s="2">
+        <v>179077140288721</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N17" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17">
+        <v>16</v>
+      </c>
+      <c r="R17" s="3">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="S17" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46295.397673611114</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18">
+        <v>2772404062</v>
+      </c>
+      <c r="G18" s="2">
+        <v>179077155992701</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" t="s">
+        <v>35</v>
+      </c>
+      <c r="N18" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18">
+        <v>16</v>
+      </c>
+      <c r="R18" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="S18" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>46295.398715277777</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19">
+        <v>2763593875</v>
+      </c>
+      <c r="G19" s="2">
+        <v>179077164994811</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" t="s">
+        <v>25</v>
+      </c>
+      <c r="O19">
+        <v>19</v>
+      </c>
+      <c r="R19" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="S19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>46295.400312500002</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20">
+        <v>2785042656</v>
+      </c>
+      <c r="G20" s="2">
+        <v>179077178697031</v>
+      </c>
+      <c r="H20" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="R20" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46295.401666666665</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21">
+        <v>2771822590</v>
+      </c>
+      <c r="G21" s="2">
+        <v>179077190499321</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" t="s">
+        <v>35</v>
+      </c>
+      <c r="N21" t="s">
+        <v>25</v>
+      </c>
+      <c r="O21">
+        <v>16</v>
+      </c>
+      <c r="R21" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="S21" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46295.403449074074</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22">
+        <v>2788244054</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1790772058102220</v>
+      </c>
+      <c r="H22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N22" t="s">
+        <v>25</v>
+      </c>
+      <c r="O22">
+        <v>16</v>
+      </c>
+      <c r="R22" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S22" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46295.404560185183</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23">
+        <v>2786543185</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1790772154104560</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" t="s">
+        <v>50</v>
+      </c>
+      <c r="N23" t="s">
+        <v>29</v>
+      </c>
+      <c r="O23">
+        <v>16</v>
+      </c>
+      <c r="R23" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="S23" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46295.406076388892</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24">
+        <v>2788244281</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1790772285106760</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" t="s">
+        <v>35</v>
+      </c>
+      <c r="N24" t="s">
+        <v>25</v>
+      </c>
+      <c r="O24">
+        <v>16</v>
+      </c>
+      <c r="R24" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="S24" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>46295.407407407409</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25">
+        <v>2770950434</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1790772399108920</v>
+      </c>
+      <c r="H25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="R25" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>46295.41</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26">
+        <v>2784460229</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1790772608111340</v>
+      </c>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26">
+        <v>17</v>
+      </c>
+      <c r="R26" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>46295.410196759258</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27">
+        <v>2784460254</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1790772633111920</v>
+      </c>
+      <c r="H27" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s">
+        <v>52</v>
+      </c>
+      <c r="J27" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" t="s">
+        <v>28</v>
+      </c>
+      <c r="N27" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27">
+        <v>17</v>
+      </c>
+      <c r="R27" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>46295.415879629632</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28">
+        <v>2762506574</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1790773097119060</v>
+      </c>
+      <c r="H28" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s">
+        <v>53</v>
+      </c>
+      <c r="J28" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>29</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="R28" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>46295.417025462964</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29">
+        <v>2762506672</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1790773195121160</v>
+      </c>
+      <c r="H29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J29" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>46295.417824074073</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30">
+        <v>2778783519</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1790773296125070</v>
+      </c>
+      <c r="H30" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" t="s">
+        <v>54</v>
+      </c>
+      <c r="J30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" t="s">
+        <v>28</v>
+      </c>
+      <c r="N30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30">
+        <v>17</v>
+      </c>
+      <c r="R30" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>46295.417974537035</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31">
+        <v>2778783532</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1790773309125460</v>
+      </c>
+      <c r="H31" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" t="s">
+        <v>54</v>
+      </c>
+      <c r="J31" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31">
+        <v>17</v>
+      </c>
+      <c r="R31" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>46295.418368055558</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32">
+        <v>2788938251</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1790773347126010</v>
+      </c>
+      <c r="H32" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J32" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" t="s">
+        <v>35</v>
+      </c>
+      <c r="N32" t="s">
+        <v>25</v>
+      </c>
+      <c r="O32">
+        <v>16</v>
+      </c>
+      <c r="R32" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S32" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>46295.419618055559</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33">
+        <v>2790586715</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1790773455129430</v>
+      </c>
+      <c r="H33" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" t="s">
+        <v>56</v>
+      </c>
+      <c r="J33" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" t="s">
+        <v>35</v>
+      </c>
+      <c r="N33" t="s">
+        <v>29</v>
+      </c>
+      <c r="O33">
+        <v>16</v>
+      </c>
+      <c r="R33" s="3">
+        <v>1.2037037037037038E-3</v>
+      </c>
+      <c r="S33" s="3">
+        <v>1.0995370370370371E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>46295.423715277779</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34">
+        <v>2762973963</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1790773809139360</v>
+      </c>
+      <c r="H34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" t="s">
+        <v>57</v>
+      </c>
+      <c r="J34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="R34" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>46295.424479166664</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35">
+        <v>2762974028</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1790773874142130</v>
+      </c>
+      <c r="H35" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" t="s">
+        <v>57</v>
+      </c>
+      <c r="J35" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>29</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="R35" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>46295.425393518519</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36">
+        <v>2762974108</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1790773953144260</v>
+      </c>
+      <c r="H36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>29</v>
+      </c>
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="R36" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>46295.426631944443</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37">
+        <v>2785430533</v>
+      </c>
+      <c r="G37" s="2">
+        <v>1790774061146830</v>
+      </c>
+      <c r="H37" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" t="s">
+        <v>86</v>
+      </c>
+      <c r="N37" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37">
+        <v>16</v>
+      </c>
+      <c r="R37" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="S37" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>46295.428124999999</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38">
+        <v>2783286973</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1790774190149790</v>
+      </c>
+      <c r="H38" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s">
+        <v>59</v>
+      </c>
+      <c r="J38" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" t="s">
+        <v>60</v>
+      </c>
+      <c r="N38" t="s">
+        <v>29</v>
+      </c>
+      <c r="O38">
+        <v>16</v>
+      </c>
+      <c r="R38" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S38" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>46295.428414351853</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39">
+        <v>2783286998</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1790774215150580</v>
+      </c>
+      <c r="H39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" t="s">
+        <v>59</v>
+      </c>
+      <c r="J39" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" t="s">
+        <v>35</v>
+      </c>
+      <c r="N39" t="s">
+        <v>25</v>
+      </c>
+      <c r="O39">
+        <v>16</v>
+      </c>
+      <c r="R39" s="3">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="S39" s="3">
+        <v>9.4907407407407408E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>46295.430231481485</v>
+      </c>
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40">
+        <v>2761743745</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1790774372154370</v>
+      </c>
+      <c r="H40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" t="s">
+        <v>23</v>
+      </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" t="s">
+        <v>35</v>
+      </c>
+      <c r="N40" t="s">
+        <v>25</v>
+      </c>
+      <c r="O40">
+        <v>16</v>
+      </c>
+      <c r="R40" s="3">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="S40" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>46295.431608796294</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41">
+        <v>2789817368</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1790774490156960</v>
+      </c>
+      <c r="H41" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" t="s">
+        <v>62</v>
+      </c>
+      <c r="J41" t="s">
+        <v>23</v>
+      </c>
+      <c r="K41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>29</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="R41" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S41" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>46295.432326388887</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42">
+        <v>2789817430</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1790774552158650</v>
+      </c>
+      <c r="H42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s">
+        <v>62</v>
+      </c>
+      <c r="J42" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>29</v>
+      </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="R42" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>46295.43240740741</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43">
+        <v>2789817436</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1790774558159100</v>
+      </c>
+      <c r="H43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" t="s">
+        <v>62</v>
+      </c>
+      <c r="J43" t="s">
+        <v>23</v>
+      </c>
+      <c r="K43" t="s">
+        <v>37</v>
+      </c>
+      <c r="N43" t="s">
+        <v>29</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="R43" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>46295.432708333334</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44">
+        <v>2782224330</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1790774585160190</v>
+      </c>
+      <c r="H44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" t="s">
+        <v>63</v>
+      </c>
+      <c r="J44" t="s">
+        <v>23</v>
+      </c>
+      <c r="K44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>29</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="R44" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S44" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>46295.432800925926</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45">
+        <v>2782224339</v>
+      </c>
+      <c r="G45" s="2">
+        <v>1790774594160390</v>
+      </c>
+      <c r="H45" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s">
+        <v>63</v>
+      </c>
+      <c r="J45" t="s">
+        <v>23</v>
+      </c>
+      <c r="K45" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" t="s">
+        <v>35</v>
+      </c>
+      <c r="N45" t="s">
+        <v>25</v>
+      </c>
+      <c r="O45">
+        <v>16</v>
+      </c>
+      <c r="R45" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="S45" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>46295.433425925927</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46">
+        <v>2782224393</v>
+      </c>
+      <c r="G46" s="2">
+        <v>1790774648162110</v>
+      </c>
+      <c r="H46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" t="s">
+        <v>63</v>
+      </c>
+      <c r="J46" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" t="s">
+        <v>35</v>
+      </c>
+      <c r="N46" t="s">
+        <v>29</v>
+      </c>
+      <c r="O46">
+        <v>16</v>
+      </c>
+      <c r="R46" s="3">
+        <v>1.6782407407407408E-3</v>
+      </c>
+      <c r="S46" s="3">
+        <v>1.4814814814814814E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>46295.436921296299</v>
+      </c>
+      <c r="B47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>2786061303</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1790774949171850</v>
+      </c>
+      <c r="H47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s">
+        <v>64</v>
+      </c>
+      <c r="J47" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>29</v>
+      </c>
+      <c r="O47">
+        <v>1</v>
+      </c>
+      <c r="R47" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S47" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>46295.436990740738</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48">
+        <v>2786061310</v>
+      </c>
+      <c r="G48" s="2">
+        <v>1790774956172100</v>
+      </c>
+      <c r="H48" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s">
+        <v>64</v>
+      </c>
+      <c r="J48" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" t="s">
+        <v>29</v>
+      </c>
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="R48" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S48" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>46295.437094907407</v>
+      </c>
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49">
+        <v>2786061319</v>
+      </c>
+      <c r="G49" s="2">
+        <v>1790774965172380</v>
+      </c>
+      <c r="H49" t="s">
+        <v>21</v>
+      </c>
+      <c r="I49" t="s">
+        <v>64</v>
+      </c>
+      <c r="J49" t="s">
+        <v>23</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" t="s">
+        <v>86</v>
+      </c>
+      <c r="N49" t="s">
+        <v>29</v>
+      </c>
+      <c r="O49">
+        <v>16</v>
+      </c>
+      <c r="R49" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="S49" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>46295.438483796293</v>
+      </c>
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50">
+        <v>2789877081</v>
+      </c>
+      <c r="G50" s="2">
+        <v>1790775084175700</v>
+      </c>
+      <c r="H50" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s">
+        <v>65</v>
+      </c>
+      <c r="J50" t="s">
+        <v>23</v>
+      </c>
+      <c r="K50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>29</v>
+      </c>
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="R50" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S50" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>46295.439189814817</v>
+      </c>
+      <c r="B51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51">
+        <v>2789877143</v>
+      </c>
+      <c r="G51" s="2">
+        <v>1790775146177490</v>
+      </c>
+      <c r="H51" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" t="s">
+        <v>65</v>
+      </c>
+      <c r="J51" t="s">
+        <v>23</v>
+      </c>
+      <c r="K51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" t="s">
+        <v>86</v>
+      </c>
+      <c r="N51" t="s">
+        <v>25</v>
+      </c>
+      <c r="O51">
+        <v>16</v>
+      </c>
+      <c r="R51" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S51" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>46295.440983796296</v>
+      </c>
+      <c r="B52" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52">
+        <v>1816662615</v>
+      </c>
+      <c r="G52" s="2">
+        <v>1790775241180710</v>
+      </c>
+      <c r="H52" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s">
+        <v>66</v>
+      </c>
+      <c r="J52" t="s">
+        <v>23</v>
+      </c>
+      <c r="K52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>29</v>
+      </c>
+      <c r="O52">
+        <v>19</v>
+      </c>
+      <c r="R52" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S52" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>46295.442395833335</v>
+      </c>
+      <c r="B53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53">
+        <v>1816662736</v>
+      </c>
+      <c r="G53" s="2">
+        <v>1790775362184320</v>
+      </c>
+      <c r="H53" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s">
+        <v>66</v>
+      </c>
+      <c r="J53" t="s">
+        <v>23</v>
+      </c>
+      <c r="K53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>29</v>
+      </c>
+      <c r="O53">
+        <v>19</v>
+      </c>
+      <c r="R53" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S53" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>46295.443113425928</v>
+      </c>
+      <c r="B54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54">
+        <v>1816662972</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1790775485187850</v>
+      </c>
+      <c r="H54" t="s">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s">
+        <v>67</v>
+      </c>
+      <c r="J54" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" t="s">
+        <v>86</v>
+      </c>
+      <c r="N54" t="s">
+        <v>29</v>
+      </c>
+      <c r="O54">
+        <v>16</v>
+      </c>
+      <c r="R54" s="3">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="S54" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>46295.447083333333</v>
+      </c>
+      <c r="B55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55">
+        <v>2782898627</v>
+      </c>
+      <c r="G55" s="2">
+        <v>1790775768195970</v>
+      </c>
+      <c r="H55" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s">
+        <v>68</v>
+      </c>
+      <c r="J55" t="s">
+        <v>23</v>
+      </c>
+      <c r="K55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>29</v>
+      </c>
+      <c r="O55">
+        <v>19</v>
+      </c>
+      <c r="R55" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S55" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>46295.448680555557</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" t="s">
+        <v>20</v>
+      </c>
+      <c r="F56">
+        <v>2782898765</v>
+      </c>
+      <c r="G56" s="2">
+        <v>1790775906199080</v>
+      </c>
+      <c r="H56" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s">
+        <v>68</v>
+      </c>
+      <c r="J56" t="s">
+        <v>23</v>
+      </c>
+      <c r="K56" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" t="s">
+        <v>29</v>
+      </c>
+      <c r="O56">
+        <v>19</v>
+      </c>
+      <c r="R56" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S56" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>46295.450613425928</v>
+      </c>
+      <c r="B57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57">
+        <v>2788680634</v>
+      </c>
+      <c r="G57" s="2">
+        <v>1790776072202820</v>
+      </c>
+      <c r="H57" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s">
+        <v>69</v>
+      </c>
+      <c r="J57" t="s">
+        <v>23</v>
+      </c>
+      <c r="K57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>29</v>
+      </c>
+      <c r="O57">
+        <v>19</v>
+      </c>
+      <c r="R57" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S57" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>46295.452060185184</v>
+      </c>
+      <c r="B58" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58">
+        <v>2788680759</v>
+      </c>
+      <c r="G58" s="2">
+        <v>1790776198205940</v>
+      </c>
+      <c r="H58" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s">
+        <v>69</v>
+      </c>
+      <c r="J58" t="s">
+        <v>23</v>
+      </c>
+      <c r="K58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>29</v>
+      </c>
+      <c r="O58">
+        <v>19</v>
+      </c>
+      <c r="R58" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S58" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>46295.452731481484</v>
+      </c>
+      <c r="B59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" t="s">
+        <v>20</v>
+      </c>
+      <c r="F59">
+        <v>2762106794</v>
+      </c>
+      <c r="G59" s="2">
+        <v>1790776316209420</v>
+      </c>
+      <c r="H59" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s">
+        <v>70</v>
+      </c>
+      <c r="J59" t="s">
+        <v>23</v>
+      </c>
+      <c r="K59" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59" t="s">
+        <v>35</v>
+      </c>
+      <c r="N59" t="s">
+        <v>29</v>
+      </c>
+      <c r="O59">
+        <v>16</v>
+      </c>
+      <c r="R59" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="S59" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>46295.453773148147</v>
+      </c>
+      <c r="B60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60">
+        <v>2762106884</v>
+      </c>
+      <c r="G60" s="2">
+        <v>1790776406212010</v>
+      </c>
+      <c r="H60" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s">
+        <v>70</v>
+      </c>
+      <c r="J60" t="s">
+        <v>23</v>
+      </c>
+      <c r="K60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" t="s">
+        <v>35</v>
+      </c>
+      <c r="N60" t="s">
+        <v>25</v>
+      </c>
+      <c r="O60">
+        <v>16</v>
+      </c>
+      <c r="R60" s="3">
+        <v>8.3333333333333339E-4</v>
+      </c>
+      <c r="S60" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>46295.455717592595</v>
+      </c>
+      <c r="B61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61">
+        <v>2772488737</v>
+      </c>
+      <c r="G61" s="2">
+        <v>1790776573216900</v>
+      </c>
+      <c r="H61" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s">
+        <v>71</v>
+      </c>
+      <c r="J61" t="s">
+        <v>23</v>
+      </c>
+      <c r="K61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>29</v>
+      </c>
+      <c r="O61">
+        <v>1</v>
+      </c>
+      <c r="R61" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S61" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>46295.455787037034</v>
+      </c>
+      <c r="B62" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62">
+        <v>2772488744</v>
+      </c>
+      <c r="G62" s="2">
+        <v>1790776580217160</v>
+      </c>
+      <c r="H62" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s">
+        <v>71</v>
+      </c>
+      <c r="J62" t="s">
+        <v>23</v>
+      </c>
+      <c r="K62" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" t="s">
+        <v>35</v>
+      </c>
+      <c r="N62" t="s">
+        <v>29</v>
+      </c>
+      <c r="O62">
+        <v>16</v>
+      </c>
+      <c r="R62" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>46295.457129629627</v>
+      </c>
+      <c r="B63" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63">
+        <v>2772488860</v>
+      </c>
+      <c r="G63" s="2">
+        <v>1790776696221090</v>
+      </c>
+      <c r="H63" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s">
+        <v>71</v>
+      </c>
+      <c r="J63" t="s">
+        <v>23</v>
+      </c>
+      <c r="K63" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" t="s">
+        <v>35</v>
+      </c>
+      <c r="N63" t="s">
+        <v>25</v>
+      </c>
+      <c r="O63">
+        <v>16</v>
+      </c>
+      <c r="R63" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="S63" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>46295.465370370373</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" t="s">
+        <v>20</v>
+      </c>
+      <c r="F64">
+        <v>2788519680</v>
+      </c>
+      <c r="G64" s="2">
+        <v>1790777408243530</v>
+      </c>
+      <c r="H64" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s">
+        <v>72</v>
+      </c>
+      <c r="J64" t="s">
+        <v>23</v>
+      </c>
+      <c r="K64" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" t="s">
+        <v>35</v>
+      </c>
+      <c r="N64" t="s">
+        <v>25</v>
+      </c>
+      <c r="O64">
+        <v>16</v>
+      </c>
+      <c r="R64" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S64" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>46295.467314814814</v>
+      </c>
+      <c r="B65" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65">
+        <v>2790773544</v>
+      </c>
+      <c r="G65" s="2">
+        <v>1790777576249750</v>
+      </c>
+      <c r="H65" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s">
+        <v>73</v>
+      </c>
+      <c r="J65" t="s">
+        <v>23</v>
+      </c>
+      <c r="K65" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" t="s">
+        <v>35</v>
+      </c>
+      <c r="N65" t="s">
+        <v>25</v>
+      </c>
+      <c r="O65">
+        <v>16</v>
+      </c>
+      <c r="R65" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S65" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>46295.477037037039</v>
+      </c>
+      <c r="B66" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66">
+        <v>2778788830</v>
+      </c>
+      <c r="G66" s="2">
+        <v>1790778380275630</v>
+      </c>
+      <c r="H66" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s">
+        <v>74</v>
+      </c>
+      <c r="J66" t="s">
+        <v>23</v>
+      </c>
+      <c r="K66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>29</v>
+      </c>
+      <c r="O66">
+        <v>1</v>
+      </c>
+      <c r="R66" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S66" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>46295.478113425925</v>
+      </c>
+      <c r="B67" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67">
+        <v>2778788959</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1790778509278760</v>
+      </c>
+      <c r="H67" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s">
+        <v>74</v>
+      </c>
+      <c r="J67" t="s">
+        <v>23</v>
+      </c>
+      <c r="K67" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67" t="s">
+        <v>35</v>
+      </c>
+      <c r="N67" t="s">
+        <v>29</v>
+      </c>
+      <c r="O67">
+        <v>16</v>
+      </c>
+      <c r="R67" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S67" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>46295.479814814818</v>
+      </c>
+      <c r="B68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68">
+        <v>2789660630</v>
+      </c>
+      <c r="G68" s="2">
+        <v>1790778656281060</v>
+      </c>
+      <c r="H68" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s">
+        <v>75</v>
+      </c>
+      <c r="J68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K68" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N68" t="s">
+        <v>25</v>
+      </c>
+      <c r="O68">
+        <v>16</v>
+      </c>
+      <c r="R68" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="S68" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>46295.485555555555</v>
+      </c>
+      <c r="B69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69">
+        <v>2772312455</v>
+      </c>
+      <c r="G69" s="2">
+        <v>1790779152285100</v>
+      </c>
+      <c r="H69" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s">
+        <v>76</v>
+      </c>
+      <c r="J69" t="s">
+        <v>23</v>
+      </c>
+      <c r="K69" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" t="s">
+        <v>25</v>
+      </c>
+      <c r="O69">
+        <v>16</v>
+      </c>
+      <c r="R69" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S69" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>46295.494803240741</v>
+      </c>
+      <c r="B70" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70">
+        <v>2769943636</v>
+      </c>
+      <c r="G70" s="2">
+        <v>1790779951291120</v>
+      </c>
+      <c r="H70" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s">
+        <v>41</v>
+      </c>
+      <c r="J70" t="s">
+        <v>23</v>
+      </c>
+      <c r="K70" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70" t="s">
+        <v>35</v>
+      </c>
+      <c r="N70" t="s">
+        <v>29</v>
+      </c>
+      <c r="O70">
+        <v>16</v>
+      </c>
+      <c r="R70" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S70" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>46295.495752314811</v>
+      </c>
+      <c r="B71" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" t="s">
+        <v>20</v>
+      </c>
+      <c r="F71">
+        <v>2769943717</v>
+      </c>
+      <c r="G71" s="2">
+        <v>1790780033291630</v>
+      </c>
+      <c r="H71" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s">
+        <v>41</v>
+      </c>
+      <c r="J71" t="s">
+        <v>23</v>
+      </c>
+      <c r="K71" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71" t="s">
+        <v>35</v>
+      </c>
+      <c r="N71" t="s">
+        <v>29</v>
+      </c>
+      <c r="O71">
+        <v>16</v>
+      </c>
+      <c r="R71" s="3">
+        <v>1.0763888888888889E-3</v>
+      </c>
+      <c r="S71" s="3">
+        <v>1.0300925925925926E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>46295.503437500003</v>
+      </c>
+      <c r="B72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72">
+        <v>2790699569</v>
+      </c>
+      <c r="G72" s="2">
+        <v>1790780696302180</v>
+      </c>
+      <c r="H72" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72" t="s">
+        <v>23</v>
+      </c>
+      <c r="K72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>29</v>
+      </c>
+      <c r="O72">
+        <v>1</v>
+      </c>
+      <c r="R72" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S72" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>46295.504189814812</v>
+      </c>
+      <c r="B73" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73">
+        <v>2790699635</v>
+      </c>
+      <c r="G73" s="2">
+        <v>1790780762303640</v>
+      </c>
+      <c r="H73" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" t="s">
+        <v>22</v>
+      </c>
+      <c r="J73" t="s">
+        <v>23</v>
+      </c>
+      <c r="K73" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73" t="s">
+        <v>35</v>
+      </c>
+      <c r="N73" t="s">
+        <v>25</v>
+      </c>
+      <c r="O73">
+        <v>16</v>
+      </c>
+      <c r="R73" s="3">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="S73" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>46295.505613425928</v>
+      </c>
+      <c r="B74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" t="s">
+        <v>20</v>
+      </c>
+      <c r="F74">
+        <v>2790203391</v>
+      </c>
+      <c r="G74" s="2">
+        <v>1790780885305830</v>
+      </c>
+      <c r="H74" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s">
+        <v>27</v>
+      </c>
+      <c r="J74" t="s">
+        <v>23</v>
+      </c>
+      <c r="K74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>25</v>
+      </c>
+      <c r="O74">
+        <v>19</v>
+      </c>
+      <c r="R74" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="S74" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>46295.506574074076</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75">
+        <v>2777625468</v>
+      </c>
+      <c r="G75" s="2">
+        <v>1790780959307800</v>
+      </c>
+      <c r="H75" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s">
+        <v>31</v>
+      </c>
+      <c r="J75" t="s">
+        <v>23</v>
+      </c>
+      <c r="K75" t="s">
+        <v>28</v>
+      </c>
+      <c r="N75" t="s">
+        <v>29</v>
+      </c>
+      <c r="O75">
+        <v>19</v>
+      </c>
+      <c r="R75" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S75" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>46295.508287037039</v>
+      </c>
+      <c r="B76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" t="s">
+        <v>20</v>
+      </c>
+      <c r="F76">
+        <v>2779240616</v>
+      </c>
+      <c r="G76" s="2">
+        <v>1790781056310370</v>
+      </c>
+      <c r="H76" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s">
+        <v>32</v>
+      </c>
+      <c r="J76" t="s">
+        <v>23</v>
+      </c>
+      <c r="K76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>29</v>
+      </c>
+      <c r="O76">
+        <v>19</v>
+      </c>
+      <c r="R76" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S76" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>46295.509016203701</v>
+      </c>
+      <c r="B77" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77">
+        <v>2762868796</v>
+      </c>
+      <c r="G77" s="2">
+        <v>1790781179313240</v>
+      </c>
+      <c r="H77" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s">
+        <v>23</v>
+      </c>
+      <c r="K77" t="s">
+        <v>24</v>
+      </c>
+      <c r="L77" t="s">
+        <v>35</v>
+      </c>
+      <c r="N77" t="s">
+        <v>25</v>
+      </c>
+      <c r="O77">
+        <v>16</v>
+      </c>
+      <c r="R77" s="3">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="S77" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>46295.510509259257</v>
+      </c>
+      <c r="B78" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78">
+        <v>2790696898</v>
+      </c>
+      <c r="G78" s="2">
+        <v>1790781308315770</v>
+      </c>
+      <c r="H78" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s">
+        <v>33</v>
+      </c>
+      <c r="J78" t="s">
+        <v>23</v>
+      </c>
+      <c r="K78" t="s">
+        <v>24</v>
+      </c>
+      <c r="L78" t="s">
+        <v>60</v>
+      </c>
+      <c r="N78" t="s">
+        <v>25</v>
+      </c>
+      <c r="O78">
+        <v>16</v>
+      </c>
+      <c r="R78" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S78" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>46295.511493055557</v>
+      </c>
+      <c r="B79" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79">
+        <v>2780822424</v>
+      </c>
+      <c r="G79" s="2">
+        <v>1790781392317780</v>
+      </c>
+      <c r="H79" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" t="s">
+        <v>34</v>
+      </c>
+      <c r="J79" t="s">
+        <v>23</v>
+      </c>
+      <c r="K79" t="s">
+        <v>28</v>
+      </c>
+      <c r="N79" t="s">
+        <v>29</v>
+      </c>
+      <c r="O79">
+        <v>19</v>
+      </c>
+      <c r="R79" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S79" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>46295.512175925927</v>
+      </c>
+      <c r="B80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80">
+        <v>2780822484</v>
+      </c>
+      <c r="G80" s="2">
+        <v>1790781452319390</v>
+      </c>
+      <c r="H80" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" t="s">
+        <v>34</v>
+      </c>
+      <c r="J80" t="s">
+        <v>23</v>
+      </c>
+      <c r="K80" t="s">
+        <v>24</v>
+      </c>
+      <c r="L80" t="s">
+        <v>60</v>
+      </c>
+      <c r="N80" t="s">
+        <v>25</v>
+      </c>
+      <c r="O80">
+        <v>16</v>
+      </c>
+      <c r="R80" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S80" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>46295.512974537036</v>
+      </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81">
+        <v>2789855979</v>
+      </c>
+      <c r="G81" s="2">
+        <v>1790781521322020</v>
+      </c>
+      <c r="H81" t="s">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s">
+        <v>36</v>
+      </c>
+      <c r="J81" t="s">
+        <v>23</v>
+      </c>
+      <c r="K81" t="s">
+        <v>24</v>
+      </c>
+      <c r="L81" t="s">
+        <v>86</v>
+      </c>
+      <c r="N81" t="s">
+        <v>29</v>
+      </c>
+      <c r="O81">
+        <v>16</v>
+      </c>
+      <c r="R81" s="3">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="S81" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>46295.515347222223</v>
+      </c>
+      <c r="B82" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82">
+        <v>2766372257</v>
+      </c>
+      <c r="G82" s="2">
+        <v>1790781726326540</v>
+      </c>
+      <c r="H82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I82" t="s">
+        <v>38</v>
+      </c>
+      <c r="J82" t="s">
+        <v>23</v>
+      </c>
+      <c r="K82" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82" t="s">
+        <v>86</v>
+      </c>
+      <c r="N82" t="s">
+        <v>29</v>
+      </c>
+      <c r="O82">
+        <v>16</v>
+      </c>
+      <c r="R82" s="3">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="S82" s="3">
+        <v>7.8703703703703705E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>46295.517488425925</v>
+      </c>
+      <c r="B83" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83">
+        <v>2755295804</v>
+      </c>
+      <c r="G83" s="2">
+        <v>1790781867328880</v>
+      </c>
+      <c r="H83" t="s">
+        <v>21</v>
+      </c>
+      <c r="I83" t="s">
+        <v>39</v>
+      </c>
+      <c r="J83" t="s">
+        <v>23</v>
+      </c>
+      <c r="K83" t="s">
+        <v>28</v>
+      </c>
+      <c r="N83" t="s">
+        <v>29</v>
+      </c>
+      <c r="O83">
+        <v>17</v>
+      </c>
+      <c r="R83" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S83" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>46295.517754629633</v>
+      </c>
+      <c r="B84" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84">
+        <v>2755295863</v>
+      </c>
+      <c r="G84" s="2">
+        <v>1790781926330450</v>
+      </c>
+      <c r="H84" t="s">
+        <v>21</v>
+      </c>
+      <c r="I84" t="s">
+        <v>39</v>
+      </c>
+      <c r="J84" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" t="s">
+        <v>28</v>
+      </c>
+      <c r="N84" t="s">
+        <v>29</v>
+      </c>
+      <c r="O84">
+        <v>17</v>
+      </c>
+      <c r="R84" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S84" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>46295.518310185187</v>
+      </c>
+      <c r="B85" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85">
+        <v>2755295878</v>
+      </c>
+      <c r="G85" s="2">
+        <v>1790781941330820</v>
+      </c>
+      <c r="H85" t="s">
+        <v>21</v>
+      </c>
+      <c r="I85" t="s">
+        <v>39</v>
+      </c>
+      <c r="J85" t="s">
+        <v>23</v>
+      </c>
+      <c r="K85" t="s">
+        <v>28</v>
+      </c>
+      <c r="N85" t="s">
+        <v>29</v>
+      </c>
+      <c r="O85">
+        <v>17</v>
+      </c>
+      <c r="R85" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S85" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>46295.519328703704</v>
+      </c>
+      <c r="B86" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" t="s">
+        <v>20</v>
+      </c>
+      <c r="F86">
+        <v>2765946004</v>
+      </c>
+      <c r="G86" s="2">
+        <v>1790782070333980</v>
+      </c>
+      <c r="H86" t="s">
+        <v>21</v>
+      </c>
+      <c r="I86" t="s">
+        <v>40</v>
+      </c>
+      <c r="J86" t="s">
+        <v>23</v>
+      </c>
+      <c r="K86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>29</v>
+      </c>
+      <c r="O86">
+        <v>1</v>
+      </c>
+      <c r="R86" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S86" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>46295.519409722219</v>
+      </c>
+      <c r="B87" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87">
+        <v>2765946011</v>
+      </c>
+      <c r="G87" s="2">
+        <v>1790782077334210</v>
+      </c>
+      <c r="H87" t="s">
+        <v>21</v>
+      </c>
+      <c r="I87" t="s">
+        <v>40</v>
+      </c>
+      <c r="J87" t="s">
+        <v>23</v>
+      </c>
+      <c r="K87" t="s">
+        <v>24</v>
+      </c>
+      <c r="L87" t="s">
+        <v>60</v>
+      </c>
+      <c r="N87" t="s">
+        <v>25</v>
+      </c>
+      <c r="O87">
+        <v>16</v>
+      </c>
+      <c r="R87" s="3">
+        <v>1.3657407407407407E-3</v>
+      </c>
+      <c r="S87" s="3">
+        <v>1.3310185185185185E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>46295.521516203706</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F88">
+        <v>2775759927</v>
+      </c>
+      <c r="G88" s="2">
+        <v>1790782259340100</v>
+      </c>
+      <c r="H88" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" t="s">
+        <v>43</v>
+      </c>
+      <c r="J88" t="s">
+        <v>23</v>
+      </c>
+      <c r="K88" t="s">
+        <v>24</v>
+      </c>
+      <c r="L88" t="s">
+        <v>35</v>
+      </c>
+      <c r="N88" t="s">
+        <v>29</v>
+      </c>
+      <c r="O88">
+        <v>16</v>
+      </c>
+      <c r="R88" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="S88" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>46295.524328703701</v>
+      </c>
+      <c r="B89" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89">
+        <v>2770352293</v>
+      </c>
+      <c r="G89" s="2">
+        <v>1790782502345560</v>
+      </c>
+      <c r="H89" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" t="s">
+        <v>78</v>
+      </c>
+      <c r="J89" t="s">
+        <v>23</v>
+      </c>
+      <c r="K89" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" t="s">
+        <v>29</v>
+      </c>
+      <c r="O89">
+        <v>1</v>
+      </c>
+      <c r="R89" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S89" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>46295.525381944448</v>
+      </c>
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90">
+        <v>2770352356</v>
+      </c>
+      <c r="G90" s="2">
+        <v>1790782565347590</v>
+      </c>
+      <c r="H90" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90" t="s">
+        <v>78</v>
+      </c>
+      <c r="J90" t="s">
+        <v>23</v>
+      </c>
+      <c r="K90" t="s">
+        <v>37</v>
+      </c>
+      <c r="N90" t="s">
+        <v>29</v>
+      </c>
+      <c r="O90">
+        <v>1</v>
+      </c>
+      <c r="R90" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S90" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>46295.526400462964</v>
+      </c>
+      <c r="B91" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91">
+        <v>2772415184</v>
+      </c>
+      <c r="G91" s="2">
+        <v>1790782681350460</v>
+      </c>
+      <c r="H91" t="s">
+        <v>21</v>
+      </c>
+      <c r="I91" t="s">
+        <v>45</v>
+      </c>
+      <c r="J91" t="s">
+        <v>23</v>
+      </c>
+      <c r="K91" t="s">
+        <v>24</v>
+      </c>
+      <c r="L91" t="s">
+        <v>35</v>
+      </c>
+      <c r="N91" t="s">
+        <v>25</v>
+      </c>
+      <c r="O91">
+        <v>16</v>
+      </c>
+      <c r="R91" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S91" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>46295.528240740743</v>
+      </c>
+      <c r="B92" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" t="s">
+        <v>20</v>
+      </c>
+      <c r="F92">
+        <v>2763605005</v>
+      </c>
+      <c r="G92" s="2">
+        <v>1790782779352960</v>
+      </c>
+      <c r="H92" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s">
+        <v>46</v>
+      </c>
+      <c r="J92" t="s">
+        <v>23</v>
+      </c>
+      <c r="K92" t="s">
+        <v>37</v>
+      </c>
+      <c r="N92" t="s">
+        <v>29</v>
+      </c>
+      <c r="O92">
+        <v>19</v>
+      </c>
+      <c r="R92" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S92" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>46295.530115740738</v>
+      </c>
+      <c r="B93" t="s">
+        <v>19</v>
+      </c>
+      <c r="C93" t="s">
+        <v>20</v>
+      </c>
+      <c r="F93">
+        <v>2785053812</v>
+      </c>
+      <c r="G93" s="2">
+        <v>1790782942357180</v>
+      </c>
+      <c r="H93" t="s">
+        <v>21</v>
+      </c>
+      <c r="I93" t="s">
+        <v>47</v>
+      </c>
+      <c r="J93" t="s">
+        <v>23</v>
+      </c>
+      <c r="K93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>29</v>
+      </c>
+      <c r="O93">
+        <v>19</v>
+      </c>
+      <c r="R93" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S93" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>46295.531365740739</v>
+      </c>
+      <c r="B94" t="s">
+        <v>19</v>
+      </c>
+      <c r="C94" t="s">
+        <v>20</v>
+      </c>
+      <c r="F94">
+        <v>2771833796</v>
+      </c>
+      <c r="G94" s="2">
+        <v>1790783110364580</v>
+      </c>
+      <c r="H94" t="s">
+        <v>21</v>
+      </c>
+      <c r="I94" t="s">
+        <v>48</v>
+      </c>
+      <c r="J94" t="s">
+        <v>23</v>
+      </c>
+      <c r="K94" t="s">
+        <v>24</v>
+      </c>
+      <c r="L94" t="s">
+        <v>35</v>
+      </c>
+      <c r="N94" t="s">
+        <v>25</v>
+      </c>
+      <c r="O94">
+        <v>16</v>
+      </c>
+      <c r="R94" s="3">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="S94" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>46295.533634259256</v>
+      </c>
+      <c r="B95" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" t="s">
+        <v>20</v>
+      </c>
+      <c r="F95">
+        <v>2788255302</v>
+      </c>
+      <c r="G95" s="2">
+        <v>1790783306372850</v>
+      </c>
+      <c r="H95" t="s">
+        <v>21</v>
+      </c>
+      <c r="I95" t="s">
+        <v>49</v>
+      </c>
+      <c r="J95" t="s">
+        <v>23</v>
+      </c>
+      <c r="K95" t="s">
+        <v>24</v>
+      </c>
+      <c r="L95" t="s">
+        <v>35</v>
+      </c>
+      <c r="N95" t="s">
+        <v>25</v>
+      </c>
+      <c r="O95">
+        <v>16</v>
+      </c>
+      <c r="R95" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="S95" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>46295.540949074071</v>
+      </c>
+      <c r="B96" t="s">
+        <v>19</v>
+      </c>
+      <c r="C96" t="s">
+        <v>20</v>
+      </c>
+      <c r="F96">
+        <v>2770961973</v>
+      </c>
+      <c r="G96" s="2">
+        <v>1790783938396170</v>
+      </c>
+      <c r="H96" t="s">
+        <v>21</v>
+      </c>
+      <c r="I96" t="s">
+        <v>51</v>
+      </c>
+      <c r="J96" t="s">
+        <v>23</v>
+      </c>
+      <c r="K96" t="s">
+        <v>24</v>
+      </c>
+      <c r="L96" t="s">
+        <v>86</v>
+      </c>
+      <c r="N96" t="s">
+        <v>29</v>
+      </c>
+      <c r="O96">
+        <v>16</v>
+      </c>
+      <c r="R96" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="S96" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>46295.543796296297</v>
+      </c>
+      <c r="B97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" t="s">
+        <v>20</v>
+      </c>
+      <c r="F97">
+        <v>2761241051</v>
+      </c>
+      <c r="G97" s="2">
+        <v>1790784184404840</v>
+      </c>
+      <c r="H97" t="s">
+        <v>21</v>
+      </c>
+      <c r="I97" t="s">
+        <v>79</v>
+      </c>
+      <c r="J97" t="s">
+        <v>23</v>
+      </c>
+      <c r="K97" t="s">
+        <v>24</v>
+      </c>
+      <c r="L97" t="s">
+        <v>35</v>
+      </c>
+      <c r="N97" t="s">
+        <v>29</v>
+      </c>
+      <c r="O97">
+        <v>16</v>
+      </c>
+      <c r="R97" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="S97" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>46295.545451388891</v>
+      </c>
+      <c r="B98" t="s">
+        <v>19</v>
+      </c>
+      <c r="C98" t="s">
+        <v>20</v>
+      </c>
+      <c r="F98">
+        <v>2767195243</v>
+      </c>
+      <c r="G98" s="2">
+        <v>1790784266407380</v>
+      </c>
+      <c r="H98" t="s">
+        <v>21</v>
+      </c>
+      <c r="I98" t="s">
+        <v>80</v>
+      </c>
+      <c r="J98" t="s">
+        <v>23</v>
+      </c>
+      <c r="K98" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" t="s">
+        <v>29</v>
+      </c>
+      <c r="O98">
+        <v>19</v>
+      </c>
+      <c r="R98" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S98" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>46295.546122685184</v>
+      </c>
+      <c r="B99" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" t="s">
+        <v>20</v>
+      </c>
+      <c r="F99">
+        <v>2783060621</v>
+      </c>
+      <c r="G99" s="2">
+        <v>1790784385409520</v>
+      </c>
+      <c r="H99" t="s">
+        <v>21</v>
+      </c>
+      <c r="I99" t="s">
+        <v>81</v>
+      </c>
+      <c r="J99" t="s">
+        <v>23</v>
+      </c>
+      <c r="K99" t="s">
+        <v>24</v>
+      </c>
+      <c r="L99" t="s">
+        <v>60</v>
+      </c>
+      <c r="N99" t="s">
+        <v>25</v>
+      </c>
+      <c r="O99">
+        <v>16</v>
+      </c>
+      <c r="R99" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S99" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>46295.546967592592</v>
+      </c>
+      <c r="B100" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" t="s">
+        <v>20</v>
+      </c>
+      <c r="F100">
+        <v>2781788763</v>
+      </c>
+      <c r="G100" s="2">
+        <v>1790784458411700</v>
+      </c>
+      <c r="H100" t="s">
+        <v>21</v>
+      </c>
+      <c r="I100" t="s">
+        <v>82</v>
+      </c>
+      <c r="J100" t="s">
+        <v>23</v>
+      </c>
+      <c r="K100" t="s">
+        <v>24</v>
+      </c>
+      <c r="L100" t="s">
+        <v>60</v>
+      </c>
+      <c r="N100" t="s">
+        <v>25</v>
+      </c>
+      <c r="O100">
+        <v>16</v>
+      </c>
+      <c r="R100" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S100" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>46295.548148148147</v>
+      </c>
+      <c r="B101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" t="s">
+        <v>20</v>
+      </c>
+      <c r="F101">
+        <v>2781785653</v>
+      </c>
+      <c r="G101" s="2">
+        <v>1790784560415200</v>
+      </c>
+      <c r="H101" t="s">
+        <v>21</v>
+      </c>
+      <c r="I101" t="s">
+        <v>83</v>
+      </c>
+      <c r="J101" t="s">
+        <v>23</v>
+      </c>
+      <c r="K101" t="s">
+        <v>24</v>
+      </c>
+      <c r="L101" t="s">
+        <v>86</v>
+      </c>
+      <c r="N101" t="s">
+        <v>29</v>
+      </c>
+      <c r="O101">
+        <v>16</v>
+      </c>
+      <c r="R101" s="3">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="S101" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>46295.560324074075</v>
+      </c>
+      <c r="B102" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" t="s">
+        <v>20</v>
+      </c>
+      <c r="F102">
+        <v>2784473232</v>
+      </c>
+      <c r="G102" s="2">
+        <v>1790785611444720</v>
+      </c>
+      <c r="H102" t="s">
+        <v>21</v>
+      </c>
+      <c r="I102" t="s">
+        <v>52</v>
+      </c>
+      <c r="J102" t="s">
+        <v>23</v>
+      </c>
+      <c r="K102" t="s">
+        <v>37</v>
+      </c>
+      <c r="N102" t="s">
+        <v>29</v>
+      </c>
+      <c r="O102">
+        <v>1</v>
+      </c>
+      <c r="R102" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S102" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>46295.566516203704</v>
+      </c>
+      <c r="B103" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" t="s">
+        <v>20</v>
+      </c>
+      <c r="F103">
+        <v>2784473768</v>
+      </c>
+      <c r="G103" s="2">
+        <v>1790786147460030</v>
+      </c>
+      <c r="H103" t="s">
+        <v>21</v>
+      </c>
+      <c r="I103" t="s">
+        <v>52</v>
+      </c>
+      <c r="J103" t="s">
+        <v>23</v>
+      </c>
+      <c r="K103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N103" t="s">
+        <v>25</v>
+      </c>
+      <c r="O103">
+        <v>19</v>
+      </c>
+      <c r="R103" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="S103" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>46295.578819444447</v>
+      </c>
+      <c r="B104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" t="s">
+        <v>20</v>
+      </c>
+      <c r="F104">
+        <v>2781788302</v>
+      </c>
+      <c r="G104" s="2">
+        <v>1790787209482590</v>
+      </c>
+      <c r="H104" t="s">
+        <v>21</v>
+      </c>
+      <c r="I104" t="s">
+        <v>83</v>
+      </c>
+      <c r="J104" t="s">
+        <v>23</v>
+      </c>
+      <c r="K104" t="s">
+        <v>37</v>
+      </c>
+      <c r="N104" t="s">
+        <v>29</v>
+      </c>
+      <c r="O104">
+        <v>1</v>
+      </c>
+      <c r="R104" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S104" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>46295.580381944441</v>
+      </c>
+      <c r="B105" t="s">
+        <v>19</v>
+      </c>
+      <c r="C105" t="s">
+        <v>20</v>
+      </c>
+      <c r="F105">
+        <v>2762520761</v>
+      </c>
+      <c r="G105" s="2">
+        <v>1790787284484390</v>
+      </c>
+      <c r="H105" t="s">
+        <v>21</v>
+      </c>
+      <c r="I105" t="s">
+        <v>53</v>
+      </c>
+      <c r="J105" t="s">
+        <v>23</v>
+      </c>
+      <c r="K105" t="s">
+        <v>37</v>
+      </c>
+      <c r="N105" t="s">
+        <v>29</v>
+      </c>
+      <c r="O105">
+        <v>19</v>
+      </c>
+      <c r="R105" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S105" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>46295.582789351851</v>
+      </c>
+      <c r="B106" t="s">
+        <v>19</v>
+      </c>
+      <c r="C106" t="s">
+        <v>20</v>
+      </c>
+      <c r="F106">
+        <v>2778797716</v>
+      </c>
+      <c r="G106" s="2">
+        <v>1790787493489410</v>
+      </c>
+      <c r="H106" t="s">
+        <v>21</v>
+      </c>
+      <c r="I106" t="s">
+        <v>54</v>
+      </c>
+      <c r="J106" t="s">
+        <v>23</v>
+      </c>
+      <c r="K106" t="s">
+        <v>37</v>
+      </c>
+      <c r="N106" t="s">
+        <v>29</v>
+      </c>
+      <c r="O106">
+        <v>19</v>
+      </c>
+      <c r="R106" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S106" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>46295.62672453704</v>
+      </c>
+      <c r="B107" t="s">
+        <v>19</v>
+      </c>
+      <c r="C107" t="s">
+        <v>20</v>
+      </c>
+      <c r="F107">
+        <v>2788956253</v>
+      </c>
+      <c r="G107" s="2">
+        <v>1790791349609440</v>
+      </c>
+      <c r="H107" t="s">
+        <v>21</v>
+      </c>
+      <c r="I107" t="s">
+        <v>55</v>
+      </c>
+      <c r="J107" t="s">
+        <v>23</v>
+      </c>
+      <c r="K107" t="s">
+        <v>24</v>
+      </c>
+      <c r="L107" t="s">
+        <v>85</v>
+      </c>
+      <c r="N107" t="s">
+        <v>29</v>
+      </c>
+      <c r="O107">
+        <v>16</v>
+      </c>
+      <c r="R107" s="3">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="S107" s="3">
+        <v>6.7129629629629625E-4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>46295.629050925927</v>
+      </c>
+      <c r="B108" t="s">
+        <v>19</v>
+      </c>
+      <c r="C108" t="s">
+        <v>20</v>
+      </c>
+      <c r="F108">
+        <v>2769955234</v>
+      </c>
+      <c r="G108" s="2">
+        <v>1790791550615500</v>
+      </c>
+      <c r="H108" t="s">
+        <v>21</v>
+      </c>
+      <c r="I108" t="s">
+        <v>41</v>
+      </c>
+      <c r="J108" t="s">
+        <v>23</v>
+      </c>
+      <c r="K108" t="s">
+        <v>24</v>
+      </c>
+      <c r="L108" t="s">
+        <v>60</v>
+      </c>
+      <c r="N108" t="s">
+        <v>29</v>
+      </c>
+      <c r="O108">
+        <v>16</v>
+      </c>
+      <c r="R108" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="S108" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>46295.629386574074</v>
+      </c>
+      <c r="B109" t="s">
+        <v>19</v>
+      </c>
+      <c r="C109" t="s">
+        <v>20</v>
+      </c>
+      <c r="F109">
+        <v>2769955263</v>
+      </c>
+      <c r="G109" s="2">
+        <v>1790791579616630</v>
+      </c>
+      <c r="H109" t="s">
+        <v>21</v>
+      </c>
+      <c r="I109" t="s">
+        <v>41</v>
+      </c>
+      <c r="J109" t="s">
+        <v>23</v>
+      </c>
+      <c r="K109" t="s">
+        <v>24</v>
+      </c>
+      <c r="L109" t="s">
+        <v>87</v>
+      </c>
+      <c r="N109" t="s">
+        <v>29</v>
+      </c>
+      <c r="O109">
+        <v>16</v>
+      </c>
+      <c r="R109" s="3">
+        <v>1.7013888888888888E-3</v>
+      </c>
+      <c r="S109" s="3">
+        <v>1.6666666666666668E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>46295.635648148149</v>
+      </c>
+      <c r="B110" t="s">
+        <v>19</v>
+      </c>
+      <c r="C110" t="s">
+        <v>20</v>
+      </c>
+      <c r="F110">
+        <v>2759578544</v>
+      </c>
+      <c r="G110" s="2">
+        <v>1790792120634310</v>
+      </c>
+      <c r="H110" t="s">
+        <v>21</v>
+      </c>
+      <c r="I110" t="s">
+        <v>84</v>
+      </c>
+      <c r="J110" t="s">
+        <v>23</v>
+      </c>
+      <c r="K110" t="s">
+        <v>24</v>
+      </c>
+      <c r="L110" t="s">
+        <v>86</v>
+      </c>
+      <c r="N110" t="s">
+        <v>25</v>
+      </c>
+      <c r="O110">
+        <v>16</v>
+      </c>
+      <c r="R110" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S110" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>46295.637708333335</v>
+      </c>
+      <c r="B111" t="s">
+        <v>19</v>
+      </c>
+      <c r="C111" t="s">
+        <v>20</v>
+      </c>
+      <c r="F111">
+        <v>2770362028</v>
+      </c>
+      <c r="G111" s="2">
+        <v>1790792237638290</v>
+      </c>
+      <c r="H111" t="s">
+        <v>21</v>
+      </c>
+      <c r="I111" t="s">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s">
+        <v>23</v>
+      </c>
+      <c r="K111" t="s">
+        <v>37</v>
+      </c>
+      <c r="N111" t="s">
+        <v>29</v>
+      </c>
+      <c r="O111">
+        <v>19</v>
+      </c>
+      <c r="R111" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S111" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>46295.638402777775</v>
+      </c>
+      <c r="B112" t="s">
+        <v>19</v>
+      </c>
+      <c r="C112" t="s">
+        <v>20</v>
+      </c>
+      <c r="F112">
+        <v>2790605618</v>
+      </c>
+      <c r="G112" s="2">
+        <v>1790792358643080</v>
+      </c>
+      <c r="H112" t="s">
+        <v>21</v>
+      </c>
+      <c r="I112" t="s">
+        <v>56</v>
+      </c>
+      <c r="J112" t="s">
+        <v>23</v>
+      </c>
+      <c r="K112" t="s">
+        <v>24</v>
+      </c>
+      <c r="L112" t="s">
+        <v>86</v>
+      </c>
+      <c r="N112" t="s">
+        <v>25</v>
+      </c>
+      <c r="O112">
+        <v>16</v>
+      </c>
+      <c r="R112" s="3">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="S112" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>46295.64439814815</v>
+      </c>
+      <c r="B113" t="s">
+        <v>19</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+      <c r="F113">
+        <v>2762993024</v>
+      </c>
+      <c r="G113" s="2">
+        <v>1790792870660160</v>
+      </c>
+      <c r="H113" t="s">
+        <v>21</v>
+      </c>
+      <c r="I113" t="s">
+        <v>57</v>
+      </c>
+      <c r="J113" t="s">
+        <v>23</v>
+      </c>
+      <c r="K113" t="s">
+        <v>37</v>
+      </c>
+      <c r="N113" t="s">
+        <v>29</v>
+      </c>
+      <c r="O113">
+        <v>1</v>
+      </c>
+      <c r="R113" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S113" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>46295.645104166666</v>
+      </c>
+      <c r="B114" t="s">
+        <v>19</v>
+      </c>
+      <c r="C114" t="s">
+        <v>20</v>
+      </c>
+      <c r="F114">
+        <v>2762993090</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1790792936662700</v>
+      </c>
+      <c r="H114" t="s">
+        <v>21</v>
+      </c>
+      <c r="I114" t="s">
+        <v>57</v>
+      </c>
+      <c r="J114" t="s">
+        <v>23</v>
+      </c>
+      <c r="K114" t="s">
+        <v>37</v>
+      </c>
+      <c r="N114" t="s">
+        <v>29</v>
+      </c>
+      <c r="O114">
+        <v>1</v>
+      </c>
+      <c r="R114" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S114" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>46295.645844907405</v>
+      </c>
+      <c r="B115" t="s">
+        <v>19</v>
+      </c>
+      <c r="C115" t="s">
+        <v>20</v>
+      </c>
+      <c r="F115">
+        <v>2762993154</v>
+      </c>
+      <c r="G115" s="2">
+        <v>1790793000664690</v>
+      </c>
+      <c r="H115" t="s">
+        <v>21</v>
+      </c>
+      <c r="I115" t="s">
+        <v>57</v>
+      </c>
+      <c r="J115" t="s">
+        <v>23</v>
+      </c>
+      <c r="K115" t="s">
+        <v>37</v>
+      </c>
+      <c r="N115" t="s">
+        <v>29</v>
+      </c>
+      <c r="O115">
+        <v>1</v>
+      </c>
+      <c r="R115" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S115" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>46295.645914351851</v>
+      </c>
+      <c r="B116" t="s">
+        <v>19</v>
+      </c>
+      <c r="C116" t="s">
+        <v>20</v>
+      </c>
+      <c r="F116">
+        <v>2762993160</v>
+      </c>
+      <c r="G116" s="2">
+        <v>1790793006664930</v>
+      </c>
+      <c r="H116" t="s">
+        <v>21</v>
+      </c>
+      <c r="I116" t="s">
+        <v>57</v>
+      </c>
+      <c r="J116" t="s">
+        <v>23</v>
+      </c>
+      <c r="K116" t="s">
+        <v>37</v>
+      </c>
+      <c r="N116" t="s">
+        <v>29</v>
+      </c>
+      <c r="O116">
+        <v>1</v>
+      </c>
+      <c r="R116" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S116" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>46295.645983796298</v>
+      </c>
+      <c r="B117" t="s">
+        <v>19</v>
+      </c>
+      <c r="C117" t="s">
+        <v>20</v>
+      </c>
+      <c r="F117">
+        <v>2762993166</v>
+      </c>
+      <c r="G117" s="2">
+        <v>1790793012665160</v>
+      </c>
+      <c r="H117" t="s">
+        <v>21</v>
+      </c>
+      <c r="I117" t="s">
+        <v>57</v>
+      </c>
+      <c r="J117" t="s">
+        <v>23</v>
+      </c>
+      <c r="K117" t="s">
+        <v>37</v>
+      </c>
+      <c r="N117" t="s">
+        <v>29</v>
+      </c>
+      <c r="O117">
+        <v>1</v>
+      </c>
+      <c r="R117" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S117" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>46295.646053240744</v>
+      </c>
+      <c r="B118" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118" t="s">
+        <v>20</v>
+      </c>
+      <c r="F118">
+        <v>2762993172</v>
+      </c>
+      <c r="G118" s="2">
+        <v>1790793018665250</v>
+      </c>
+      <c r="H118" t="s">
+        <v>21</v>
+      </c>
+      <c r="I118" t="s">
+        <v>57</v>
+      </c>
+      <c r="J118" t="s">
+        <v>23</v>
+      </c>
+      <c r="K118" t="s">
+        <v>37</v>
+      </c>
+      <c r="N118" t="s">
+        <v>29</v>
+      </c>
+      <c r="O118">
+        <v>1</v>
+      </c>
+      <c r="R118" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S118" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>46295.646782407406</v>
+      </c>
+      <c r="B119" t="s">
+        <v>19</v>
+      </c>
+      <c r="C119" t="s">
+        <v>20</v>
+      </c>
+      <c r="F119">
+        <v>2783305864</v>
+      </c>
+      <c r="G119" s="2">
+        <v>1790793081668190</v>
+      </c>
+      <c r="H119" t="s">
+        <v>21</v>
+      </c>
+      <c r="I119" t="s">
+        <v>59</v>
+      </c>
+      <c r="J119" t="s">
+        <v>23</v>
+      </c>
+      <c r="K119" t="s">
+        <v>37</v>
+      </c>
+      <c r="N119" t="s">
+        <v>29</v>
+      </c>
+      <c r="O119">
+        <v>1</v>
+      </c>
+      <c r="R119" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S119" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>46295.646851851852</v>
+      </c>
+      <c r="B120" t="s">
+        <v>19</v>
+      </c>
+      <c r="C120" t="s">
+        <v>20</v>
+      </c>
+      <c r="F120">
+        <v>2783305871</v>
+      </c>
+      <c r="G120" s="2">
+        <v>1790793088668330</v>
+      </c>
+      <c r="H120" t="s">
+        <v>21</v>
+      </c>
+      <c r="I120" t="s">
+        <v>59</v>
+      </c>
+      <c r="J120" t="s">
+        <v>23</v>
+      </c>
+      <c r="K120" t="s">
+        <v>37</v>
+      </c>
+      <c r="N120" t="s">
+        <v>29</v>
+      </c>
+      <c r="O120">
+        <v>1</v>
+      </c>
+      <c r="R120" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S120" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>46295.646921296298</v>
+      </c>
+      <c r="B121" t="s">
+        <v>19</v>
+      </c>
+      <c r="C121" t="s">
+        <v>20</v>
+      </c>
+      <c r="F121">
+        <v>2783305877</v>
+      </c>
+      <c r="G121" s="2">
+        <v>1790793094668540</v>
+      </c>
+      <c r="H121" t="s">
+        <v>21</v>
+      </c>
+      <c r="I121" t="s">
+        <v>59</v>
+      </c>
+      <c r="J121" t="s">
+        <v>23</v>
+      </c>
+      <c r="K121" t="s">
+        <v>24</v>
+      </c>
+      <c r="L121" t="s">
+        <v>35</v>
+      </c>
+      <c r="N121" t="s">
+        <v>29</v>
+      </c>
+      <c r="O121">
+        <v>16</v>
+      </c>
+      <c r="R121" s="3">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="S121" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>46295.655462962961</v>
+      </c>
+      <c r="B122" t="s">
+        <v>19</v>
+      </c>
+      <c r="C122" t="s">
+        <v>20</v>
+      </c>
+      <c r="F122">
+        <v>2761763205</v>
+      </c>
+      <c r="G122" s="2">
+        <v>1790793832688900</v>
+      </c>
+      <c r="H122" t="s">
+        <v>21</v>
+      </c>
+      <c r="I122" t="s">
+        <v>61</v>
+      </c>
+      <c r="J122" t="s">
+        <v>23</v>
+      </c>
+      <c r="K122" t="s">
+        <v>24</v>
+      </c>
+      <c r="L122" t="s">
+        <v>35</v>
+      </c>
+      <c r="N122" t="s">
+        <v>25</v>
+      </c>
+      <c r="O122">
+        <v>16</v>
+      </c>
+      <c r="R122" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S122" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>46295.655682870369</v>
+      </c>
+      <c r="B123" t="s">
+        <v>19</v>
+      </c>
+      <c r="C123" t="s">
+        <v>20</v>
+      </c>
+      <c r="F123">
+        <v>2761763223</v>
+      </c>
+      <c r="G123" s="2">
+        <v>1790793850688940</v>
+      </c>
+      <c r="H123" t="s">
+        <v>21</v>
+      </c>
+      <c r="I123" t="s">
+        <v>61</v>
+      </c>
+      <c r="J123" t="s">
+        <v>23</v>
+      </c>
+      <c r="K123" t="s">
+        <v>37</v>
+      </c>
+      <c r="N123" t="s">
+        <v>29</v>
+      </c>
+      <c r="O123">
+        <v>1</v>
+      </c>
+      <c r="R123" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S123" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>46295.656261574077</v>
+      </c>
+      <c r="B124" t="s">
+        <v>19</v>
+      </c>
+      <c r="C124" t="s">
+        <v>20</v>
+      </c>
+      <c r="F124">
+        <v>2761763274</v>
+      </c>
+      <c r="G124" s="2">
+        <v>1790793901689190</v>
+      </c>
+      <c r="H124" t="s">
+        <v>21</v>
+      </c>
+      <c r="I124" t="s">
+        <v>61</v>
+      </c>
+      <c r="J124" t="s">
+        <v>23</v>
+      </c>
+      <c r="K124" t="s">
+        <v>24</v>
+      </c>
+      <c r="L124" t="s">
+        <v>35</v>
+      </c>
+      <c r="N124" t="s">
+        <v>25</v>
+      </c>
+      <c r="O124">
+        <v>16</v>
+      </c>
+      <c r="R124" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S124" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>46295.656574074077</v>
+      </c>
+      <c r="B125" t="s">
+        <v>19</v>
+      </c>
+      <c r="C125" t="s">
+        <v>20</v>
+      </c>
+      <c r="F125">
+        <v>2761763301</v>
+      </c>
+      <c r="G125" s="2">
+        <v>1790793928689300</v>
+      </c>
+      <c r="H125" t="s">
+        <v>21</v>
+      </c>
+      <c r="I125" t="s">
+        <v>61</v>
+      </c>
+      <c r="J125" t="s">
+        <v>23</v>
+      </c>
+      <c r="K125" t="s">
+        <v>24</v>
+      </c>
+      <c r="L125" t="s">
+        <v>35</v>
+      </c>
+      <c r="N125" t="s">
+        <v>29</v>
+      </c>
+      <c r="O125">
+        <v>16</v>
+      </c>
+      <c r="R125" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S125" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>46295.656990740739</v>
+      </c>
+      <c r="B126" t="s">
+        <v>19</v>
+      </c>
+      <c r="C126" t="s">
+        <v>20</v>
+      </c>
+      <c r="F126">
+        <v>2761763337</v>
+      </c>
+      <c r="G126" s="2">
+        <v>1790793964690040</v>
+      </c>
+      <c r="H126" t="s">
+        <v>21</v>
+      </c>
+      <c r="I126" t="s">
+        <v>61</v>
+      </c>
+      <c r="J126" t="s">
+        <v>23</v>
+      </c>
+      <c r="K126" t="s">
+        <v>24</v>
+      </c>
+      <c r="L126" t="s">
+        <v>35</v>
+      </c>
+      <c r="N126" t="s">
+        <v>25</v>
+      </c>
+      <c r="O126">
+        <v>16</v>
+      </c>
+      <c r="R126" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S126" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>46295.657881944448</v>
+      </c>
+      <c r="B127" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127" t="s">
+        <v>20</v>
+      </c>
+      <c r="F127">
+        <v>2789836918</v>
+      </c>
+      <c r="G127" s="2">
+        <v>1790794040690240</v>
+      </c>
+      <c r="H127" t="s">
+        <v>21</v>
+      </c>
+      <c r="I127" t="s">
+        <v>62</v>
+      </c>
+      <c r="J127" t="s">
+        <v>23</v>
+      </c>
+      <c r="K127" t="s">
+        <v>37</v>
+      </c>
+      <c r="N127" t="s">
+        <v>29</v>
+      </c>
+      <c r="O127">
+        <v>1</v>
+      </c>
+      <c r="R127" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S127" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>46295.658668981479</v>
+      </c>
+      <c r="B128" t="s">
+        <v>19</v>
+      </c>
+      <c r="C128" t="s">
+        <v>20</v>
+      </c>
+      <c r="F128">
+        <v>2789836986</v>
+      </c>
+      <c r="G128" s="2">
+        <v>1790794108690320</v>
+      </c>
+      <c r="H128" t="s">
+        <v>21</v>
+      </c>
+      <c r="I128" t="s">
+        <v>62</v>
+      </c>
+      <c r="J128" t="s">
+        <v>23</v>
+      </c>
+      <c r="K128" t="s">
+        <v>37</v>
+      </c>
+      <c r="N128" t="s">
+        <v>29</v>
+      </c>
+      <c r="O128">
+        <v>1</v>
+      </c>
+      <c r="R128" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S128" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>46295.659537037034</v>
+      </c>
+      <c r="B129" t="s">
+        <v>19</v>
+      </c>
+      <c r="C129" t="s">
+        <v>20</v>
+      </c>
+      <c r="F129">
+        <v>2789837061</v>
+      </c>
+      <c r="G129" s="2">
+        <v>1790794183690550</v>
+      </c>
+      <c r="H129" t="s">
+        <v>21</v>
+      </c>
+      <c r="I129" t="s">
+        <v>62</v>
+      </c>
+      <c r="J129" t="s">
+        <v>23</v>
+      </c>
+      <c r="K129" t="s">
+        <v>37</v>
+      </c>
+      <c r="N129" t="s">
+        <v>29</v>
+      </c>
+      <c r="O129">
+        <v>1</v>
+      </c>
+      <c r="R129" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S129" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>46295.660243055558</v>
+      </c>
+      <c r="B130" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130" t="s">
+        <v>20</v>
+      </c>
+      <c r="F130">
+        <v>2782243988</v>
+      </c>
+      <c r="G130" s="2">
+        <v>1790794243691960</v>
+      </c>
+      <c r="H130" t="s">
+        <v>21</v>
+      </c>
+      <c r="I130" t="s">
+        <v>63</v>
+      </c>
+      <c r="J130" t="s">
+        <v>23</v>
+      </c>
+      <c r="K130" t="s">
+        <v>37</v>
+      </c>
+      <c r="N130" t="s">
+        <v>29</v>
+      </c>
+      <c r="O130">
+        <v>1</v>
+      </c>
+      <c r="R130" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S130" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>46295.661979166667</v>
+      </c>
+      <c r="B131" t="s">
+        <v>19</v>
+      </c>
+      <c r="C131" t="s">
+        <v>20</v>
+      </c>
+      <c r="F131">
+        <v>1816681769</v>
+      </c>
+      <c r="G131" s="2">
+        <v>1790794395695850</v>
+      </c>
+      <c r="H131" t="s">
+        <v>21</v>
+      </c>
+      <c r="I131" t="s">
+        <v>66</v>
+      </c>
+      <c r="J131" t="s">
+        <v>23</v>
+      </c>
+      <c r="K131" t="s">
+        <v>24</v>
+      </c>
+      <c r="L131" t="s">
+        <v>86</v>
+      </c>
+      <c r="N131" t="s">
+        <v>29</v>
+      </c>
+      <c r="O131">
+        <v>16</v>
+      </c>
+      <c r="R131" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="S131" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>46295.664618055554</v>
+      </c>
+      <c r="B132" t="s">
+        <v>19</v>
+      </c>
+      <c r="C132" t="s">
+        <v>20</v>
+      </c>
+      <c r="F132">
+        <v>2782917422</v>
+      </c>
+      <c r="G132" s="2">
+        <v>1790794563701260</v>
+      </c>
+      <c r="H132" t="s">
+        <v>21</v>
+      </c>
+      <c r="I132" t="s">
+        <v>68</v>
+      </c>
+      <c r="J132" t="s">
+        <v>23</v>
+      </c>
+      <c r="K132" t="s">
+        <v>37</v>
+      </c>
+      <c r="N132" t="s">
+        <v>29</v>
+      </c>
+      <c r="O132">
+        <v>19</v>
+      </c>
+      <c r="R132" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S132" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>46295.666018518517</v>
+      </c>
+      <c r="B133" t="s">
+        <v>19</v>
+      </c>
+      <c r="C133" t="s">
+        <v>20</v>
+      </c>
+      <c r="F133">
+        <v>2782917542</v>
+      </c>
+      <c r="G133" s="2">
+        <v>1790794683705040</v>
+      </c>
+      <c r="H133" t="s">
+        <v>21</v>
+      </c>
+      <c r="I133" t="s">
+        <v>68</v>
+      </c>
+      <c r="J133" t="s">
+        <v>23</v>
+      </c>
+      <c r="K133" t="s">
+        <v>37</v>
+      </c>
+      <c r="N133" t="s">
+        <v>29</v>
+      </c>
+      <c r="O133">
+        <v>19</v>
+      </c>
+      <c r="R133" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S133" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>46295.667824074073</v>
+      </c>
+      <c r="B134" t="s">
+        <v>19</v>
+      </c>
+      <c r="C134" t="s">
+        <v>20</v>
+      </c>
+      <c r="F134">
+        <v>2788699461</v>
+      </c>
+      <c r="G134" s="2">
+        <v>1790794900709960</v>
+      </c>
+      <c r="H134" t="s">
+        <v>21</v>
+      </c>
+      <c r="I134" t="s">
+        <v>69</v>
+      </c>
+      <c r="J134" t="s">
+        <v>23</v>
+      </c>
+      <c r="K134" t="s">
+        <v>24</v>
+      </c>
+      <c r="L134" t="s">
+        <v>35</v>
+      </c>
+      <c r="N134" t="s">
+        <v>29</v>
+      </c>
+      <c r="O134">
+        <v>16</v>
+      </c>
+      <c r="R134" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="S134" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>46295.668865740743</v>
+      </c>
+      <c r="B135" t="s">
+        <v>19</v>
+      </c>
+      <c r="C135" t="s">
+        <v>20</v>
+      </c>
+      <c r="F135">
+        <v>2762125468</v>
+      </c>
+      <c r="G135" s="2">
+        <v>1790794990712930</v>
+      </c>
+      <c r="H135" t="s">
+        <v>21</v>
+      </c>
+      <c r="I135" t="s">
+        <v>70</v>
+      </c>
+      <c r="J135" t="s">
+        <v>23</v>
+      </c>
+      <c r="K135" t="s">
+        <v>24</v>
+      </c>
+      <c r="L135" t="s">
+        <v>35</v>
+      </c>
+      <c r="N135" t="s">
+        <v>29</v>
+      </c>
+      <c r="O135">
+        <v>16</v>
+      </c>
+      <c r="R135" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="S135" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>46295.669756944444</v>
+      </c>
+      <c r="B136" t="s">
+        <v>19</v>
+      </c>
+      <c r="C136" t="s">
+        <v>20</v>
+      </c>
+      <c r="F136">
+        <v>2762125545</v>
+      </c>
+      <c r="G136" s="2">
+        <v>1790795067714980</v>
+      </c>
+      <c r="H136" t="s">
+        <v>21</v>
+      </c>
+      <c r="I136" t="s">
+        <v>70</v>
+      </c>
+      <c r="J136" t="s">
+        <v>23</v>
+      </c>
+      <c r="K136" t="s">
+        <v>24</v>
+      </c>
+      <c r="L136" t="s">
+        <v>35</v>
+      </c>
+      <c r="N136" t="s">
+        <v>25</v>
+      </c>
+      <c r="O136">
+        <v>16</v>
+      </c>
+      <c r="R136" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="S136" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>46295.670057870368</v>
+      </c>
+      <c r="B137" t="s">
+        <v>19</v>
+      </c>
+      <c r="C137" t="s">
+        <v>20</v>
+      </c>
+      <c r="F137">
+        <v>2762125571</v>
+      </c>
+      <c r="G137" s="2">
+        <v>1790795093715490</v>
+      </c>
+      <c r="H137" t="s">
+        <v>21</v>
+      </c>
+      <c r="I137" t="s">
+        <v>70</v>
+      </c>
+      <c r="J137" t="s">
+        <v>23</v>
+      </c>
+      <c r="K137" t="s">
+        <v>24</v>
+      </c>
+      <c r="L137" t="s">
+        <v>35</v>
+      </c>
+      <c r="N137" t="s">
+        <v>29</v>
+      </c>
+      <c r="O137">
+        <v>16</v>
+      </c>
+      <c r="R137" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S137" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>46295.671909722223</v>
+      </c>
+      <c r="B138" t="s">
+        <v>19</v>
+      </c>
+      <c r="C138" t="s">
+        <v>20</v>
+      </c>
+      <c r="F138">
+        <v>2772507417</v>
+      </c>
+      <c r="G138" s="2">
+        <v>1790795253718000</v>
+      </c>
+      <c r="H138" t="s">
+        <v>21</v>
+      </c>
+      <c r="I138" t="s">
+        <v>71</v>
+      </c>
+      <c r="J138" t="s">
+        <v>23</v>
+      </c>
+      <c r="K138" t="s">
+        <v>24</v>
+      </c>
+      <c r="L138" t="s">
+        <v>35</v>
+      </c>
+      <c r="N138" t="s">
+        <v>25</v>
+      </c>
+      <c r="O138">
+        <v>16</v>
+      </c>
+      <c r="R138" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S138" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>46295.672395833331</v>
+      </c>
+      <c r="B139" t="s">
+        <v>19</v>
+      </c>
+      <c r="C139" t="s">
+        <v>20</v>
+      </c>
+      <c r="F139">
+        <v>2772507457</v>
+      </c>
+      <c r="G139" s="2">
+        <v>1790795293718600</v>
+      </c>
+      <c r="H139" t="s">
+        <v>21</v>
+      </c>
+      <c r="I139" t="s">
+        <v>71</v>
+      </c>
+      <c r="J139" t="s">
+        <v>23</v>
+      </c>
+      <c r="K139" t="s">
+        <v>37</v>
+      </c>
+      <c r="N139" t="s">
+        <v>29</v>
+      </c>
+      <c r="O139">
+        <v>1</v>
+      </c>
+      <c r="R139" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S139" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>46295.673171296294</v>
+      </c>
+      <c r="B140" t="s">
+        <v>19</v>
+      </c>
+      <c r="C140" t="s">
+        <v>20</v>
+      </c>
+      <c r="F140">
+        <v>2788537634</v>
+      </c>
+      <c r="G140" s="2">
+        <v>1790795362719670</v>
+      </c>
+      <c r="H140" t="s">
+        <v>21</v>
+      </c>
+      <c r="I140" t="s">
+        <v>72</v>
+      </c>
+      <c r="J140" t="s">
+        <v>23</v>
+      </c>
+      <c r="K140" t="s">
+        <v>24</v>
+      </c>
+      <c r="L140" t="s">
+        <v>86</v>
+      </c>
+      <c r="N140" t="s">
+        <v>29</v>
+      </c>
+      <c r="O140">
+        <v>16</v>
+      </c>
+      <c r="R140" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="S140" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>46295.674837962964</v>
+      </c>
+      <c r="B141" t="s">
+        <v>19</v>
+      </c>
+      <c r="C141" t="s">
+        <v>20</v>
+      </c>
+      <c r="F141">
+        <v>2790791474</v>
+      </c>
+      <c r="G141" s="2">
+        <v>1790795506723790</v>
+      </c>
+      <c r="H141" t="s">
+        <v>21</v>
+      </c>
+      <c r="I141" t="s">
+        <v>73</v>
+      </c>
+      <c r="J141" t="s">
+        <v>23</v>
+      </c>
+      <c r="K141" t="s">
+        <v>37</v>
+      </c>
+      <c r="N141" t="s">
+        <v>25</v>
+      </c>
+      <c r="O141">
+        <v>19</v>
+      </c>
+      <c r="R141" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="S141" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>46295.676307870373</v>
+      </c>
+      <c r="B142" t="s">
+        <v>19</v>
+      </c>
+      <c r="C142" t="s">
+        <v>20</v>
+      </c>
+      <c r="F142">
+        <v>2778806083</v>
+      </c>
+      <c r="G142" s="2">
+        <v>1790795633726010</v>
+      </c>
+      <c r="H142" t="s">
+        <v>21</v>
+      </c>
+      <c r="I142" t="s">
+        <v>74</v>
+      </c>
+      <c r="J142" t="s">
+        <v>23</v>
+      </c>
+      <c r="K142" t="s">
+        <v>24</v>
+      </c>
+      <c r="L142" t="s">
+        <v>86</v>
+      </c>
+      <c r="N142" t="s">
+        <v>25</v>
+      </c>
+      <c r="O142">
+        <v>16</v>
+      </c>
+      <c r="R142" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="S142" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>46295.677754629629</v>
+      </c>
+      <c r="B143" t="s">
+        <v>19</v>
+      </c>
+      <c r="C143" t="s">
+        <v>20</v>
+      </c>
+      <c r="F143">
+        <v>2789677732</v>
+      </c>
+      <c r="G143" s="2">
+        <v>1790795758728580</v>
+      </c>
+      <c r="H143" t="s">
+        <v>21</v>
+      </c>
+      <c r="I143" t="s">
+        <v>75</v>
+      </c>
+      <c r="J143" t="s">
+        <v>23</v>
+      </c>
+      <c r="K143" t="s">
+        <v>24</v>
+      </c>
+      <c r="L143" t="s">
+        <v>60</v>
+      </c>
+      <c r="N143" t="s">
+        <v>25</v>
+      </c>
+      <c r="O143">
+        <v>16</v>
+      </c>
+      <c r="R143" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="S143" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>46295.679212962961</v>
+      </c>
+      <c r="B144" t="s">
+        <v>19</v>
+      </c>
+      <c r="C144" t="s">
+        <v>20</v>
+      </c>
+      <c r="F144">
+        <v>2772329187</v>
+      </c>
+      <c r="G144" s="2">
+        <v>1790795884732200</v>
+      </c>
+      <c r="H144" t="s">
+        <v>21</v>
+      </c>
+      <c r="I144" t="s">
+        <v>76</v>
+      </c>
+      <c r="J144" t="s">
+        <v>23</v>
+      </c>
+      <c r="K144" t="s">
+        <v>24</v>
+      </c>
+      <c r="L144" t="s">
+        <v>35</v>
+      </c>
+      <c r="N144" t="s">
+        <v>25</v>
+      </c>
+      <c r="O144">
+        <v>16</v>
+      </c>
+      <c r="R144" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S144" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>46295.680138888885</v>
+      </c>
+      <c r="B145" t="s">
+        <v>19</v>
+      </c>
+      <c r="C145" t="s">
+        <v>20</v>
+      </c>
+      <c r="F145">
+        <v>2772329267</v>
+      </c>
+      <c r="G145" s="2">
+        <v>1790795964735000</v>
+      </c>
+      <c r="H145" t="s">
+        <v>21</v>
+      </c>
+      <c r="I145" t="s">
+        <v>76</v>
+      </c>
+      <c r="J145" t="s">
+        <v>23</v>
+      </c>
+      <c r="K145" t="s">
+        <v>24</v>
+      </c>
+      <c r="L145" t="s">
+        <v>35</v>
+      </c>
+      <c r="N145" t="s">
+        <v>25</v>
+      </c>
+      <c r="O145">
+        <v>16</v>
+      </c>
+      <c r="R145" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S145" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>46295.702199074076</v>
+      </c>
+      <c r="B146" t="s">
+        <v>19</v>
+      </c>
+      <c r="C146" t="s">
+        <v>20</v>
+      </c>
+      <c r="F146">
+        <v>2770367632</v>
+      </c>
+      <c r="G146" s="2">
+        <v>1790797841774700</v>
+      </c>
+      <c r="H146" t="s">
+        <v>21</v>
+      </c>
+      <c r="I146" t="s">
+        <v>78</v>
+      </c>
+      <c r="J146" t="s">
+        <v>23</v>
+      </c>
+      <c r="K146" t="s">
+        <v>28</v>
+      </c>
+      <c r="L146" t="s">
+        <v>86</v>
+      </c>
+      <c r="N146" t="s">
+        <v>29</v>
+      </c>
+      <c r="O146">
+        <v>19</v>
+      </c>
+      <c r="R146" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S146" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>46295.704641203702</v>
+      </c>
+      <c r="B147" t="s">
+        <v>19</v>
+      </c>
+      <c r="C147" t="s">
+        <v>20</v>
+      </c>
+      <c r="F147">
+        <v>2761254948</v>
+      </c>
+      <c r="G147" s="2">
+        <v>1790798081779020</v>
+      </c>
+      <c r="H147" t="s">
+        <v>21</v>
+      </c>
+      <c r="I147" t="s">
+        <v>79</v>
+      </c>
+      <c r="J147" t="s">
+        <v>23</v>
+      </c>
+      <c r="K147" t="s">
+        <v>24</v>
+      </c>
+      <c r="L147" t="s">
+        <v>35</v>
+      </c>
+      <c r="N147" t="s">
+        <v>25</v>
+      </c>
+      <c r="O147">
+        <v>16</v>
+      </c>
+      <c r="R147" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S147" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>46295.705567129633</v>
+      </c>
+      <c r="B148" t="s">
+        <v>19</v>
+      </c>
+      <c r="C148" t="s">
+        <v>20</v>
+      </c>
+      <c r="F148">
+        <v>2767209138</v>
+      </c>
+      <c r="G148" s="2">
+        <v>1790798161780380</v>
+      </c>
+      <c r="H148" t="s">
+        <v>21</v>
+      </c>
+      <c r="I148" t="s">
+        <v>80</v>
+      </c>
+      <c r="J148" t="s">
+        <v>23</v>
+      </c>
+      <c r="K148" t="s">
+        <v>24</v>
+      </c>
+      <c r="L148" t="s">
+        <v>85</v>
+      </c>
+      <c r="N148" t="s">
+        <v>29</v>
+      </c>
+      <c r="O148">
+        <v>16</v>
+      </c>
+      <c r="R148" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="S148" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>46295.70752314815</v>
+      </c>
+      <c r="B149" t="s">
+        <v>19</v>
+      </c>
+      <c r="C149" t="s">
+        <v>20</v>
+      </c>
+      <c r="F149">
+        <v>2783074566</v>
+      </c>
+      <c r="G149" s="2">
+        <v>1790798330784260</v>
+      </c>
+      <c r="H149" t="s">
+        <v>21</v>
+      </c>
+      <c r="I149" t="s">
+        <v>81</v>
+      </c>
+      <c r="J149" t="s">
+        <v>23</v>
+      </c>
+      <c r="K149" t="s">
+        <v>24</v>
+      </c>
+      <c r="L149" t="s">
+        <v>35</v>
+      </c>
+      <c r="N149" t="s">
+        <v>25</v>
+      </c>
+      <c r="O149">
+        <v>16</v>
+      </c>
+      <c r="R149" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S149" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>46295.707858796297</v>
+      </c>
+      <c r="B150" t="s">
+        <v>19</v>
+      </c>
+      <c r="C150" t="s">
+        <v>20</v>
+      </c>
+      <c r="F150">
+        <v>2783074595</v>
+      </c>
+      <c r="G150" s="2">
+        <v>1790798359785470</v>
+      </c>
+      <c r="H150" t="s">
+        <v>21</v>
+      </c>
+      <c r="I150" t="s">
+        <v>81</v>
+      </c>
+      <c r="J150" t="s">
+        <v>23</v>
+      </c>
+      <c r="K150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L150" t="s">
+        <v>35</v>
+      </c>
+      <c r="N150" t="s">
+        <v>25</v>
+      </c>
+      <c r="O150">
+        <v>16</v>
+      </c>
+      <c r="R150" s="3">
+        <v>1.6435185185185185E-3</v>
+      </c>
+      <c r="S150" s="3">
+        <v>1.6203703703703703E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>46295.717905092592</v>
+      </c>
+      <c r="B151" t="s">
+        <v>19</v>
+      </c>
+      <c r="C151" t="s">
+        <v>20</v>
+      </c>
+      <c r="F151">
+        <v>2759585651</v>
+      </c>
+      <c r="G151" s="2">
+        <v>1790799227799200</v>
+      </c>
+      <c r="H151" t="s">
+        <v>21</v>
+      </c>
+      <c r="I151" t="s">
+        <v>84</v>
+      </c>
+      <c r="J151" t="s">
+        <v>23</v>
+      </c>
+      <c r="K151" t="s">
+        <v>24</v>
+      </c>
+      <c r="L151" t="s">
+        <v>35</v>
+      </c>
+      <c r="N151" t="s">
+        <v>25</v>
+      </c>
+      <c r="O151">
+        <v>16</v>
+      </c>
+      <c r="R151" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="S151" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>46295.719513888886</v>
+      </c>
+      <c r="B152" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" t="s">
+        <v>20</v>
+      </c>
+      <c r="F152">
+        <v>2781803671</v>
+      </c>
+      <c r="G152" s="2">
+        <v>1790799366801210</v>
+      </c>
+      <c r="H152" t="s">
+        <v>21</v>
+      </c>
+      <c r="I152" t="s">
+        <v>82</v>
+      </c>
+      <c r="J152" t="s">
+        <v>23</v>
+      </c>
+      <c r="K152" t="s">
+        <v>24</v>
+      </c>
+      <c r="L152" t="s">
+        <v>86</v>
+      </c>
+      <c r="N152" t="s">
+        <v>29</v>
+      </c>
+      <c r="O152">
+        <v>16</v>
+      </c>
+      <c r="R152" s="3">
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="S152" s="3">
+        <v>1.0532407407407407E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>46296.410439814812</v>
+      </c>
+      <c r="B153" t="s">
+        <v>19</v>
+      </c>
+      <c r="C153" t="s">
+        <v>20</v>
+      </c>
+      <c r="F153">
+        <v>2790281555</v>
+      </c>
+      <c r="G153" s="2">
+        <v>179085904982711</v>
+      </c>
+      <c r="H153" t="s">
+        <v>21</v>
+      </c>
+      <c r="I153" t="s">
+        <v>27</v>
+      </c>
+      <c r="J153" t="s">
+        <v>23</v>
+      </c>
+      <c r="K153" t="s">
+        <v>28</v>
+      </c>
+      <c r="N153" t="s">
+        <v>29</v>
+      </c>
+      <c r="O153">
+        <v>19</v>
+      </c>
+      <c r="R153" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S153" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>46296.41207175926</v>
+      </c>
+      <c r="B154" t="s">
+        <v>19</v>
+      </c>
+      <c r="C154" t="s">
+        <v>20</v>
+      </c>
+      <c r="F154">
+        <v>2777703704</v>
+      </c>
+      <c r="G154" s="2">
+        <v>179085919586241</v>
+      </c>
+      <c r="H154" t="s">
+        <v>21</v>
+      </c>
+      <c r="I154" t="s">
+        <v>31</v>
+      </c>
+      <c r="J154" t="s">
+        <v>23</v>
+      </c>
+      <c r="K154" t="s">
+        <v>28</v>
+      </c>
+      <c r="N154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O154">
+        <v>19</v>
+      </c>
+      <c r="R154" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S154" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>46296.412245370368</v>
+      </c>
+      <c r="B155" t="s">
+        <v>19</v>
+      </c>
+      <c r="C155" t="s">
+        <v>20</v>
+      </c>
+      <c r="F155">
+        <v>2777703718</v>
+      </c>
+      <c r="G155" s="2">
+        <v>179085920986421</v>
+      </c>
+      <c r="H155" t="s">
+        <v>21</v>
+      </c>
+      <c r="I155" t="s">
+        <v>31</v>
+      </c>
+      <c r="J155" t="s">
+        <v>23</v>
+      </c>
+      <c r="K155" t="s">
+        <v>28</v>
+      </c>
+      <c r="N155" t="s">
+        <v>29</v>
+      </c>
+      <c r="O155">
+        <v>19</v>
+      </c>
+      <c r="R155" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S155" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>46296.412465277775</v>
+      </c>
+      <c r="B156" t="s">
+        <v>19</v>
+      </c>
+      <c r="C156" t="s">
+        <v>20</v>
+      </c>
+      <c r="F156">
+        <v>2777703746</v>
+      </c>
+      <c r="G156" s="2">
+        <v>179085923786751</v>
+      </c>
+      <c r="H156" t="s">
+        <v>21</v>
+      </c>
+      <c r="I156" t="s">
+        <v>31</v>
+      </c>
+      <c r="J156" t="s">
+        <v>23</v>
+      </c>
+      <c r="K156" t="s">
+        <v>37</v>
+      </c>
+      <c r="N156" t="s">
+        <v>25</v>
+      </c>
+      <c r="O156">
+        <v>19</v>
+      </c>
+      <c r="R156" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S156" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>46296.413275462961</v>
+      </c>
+      <c r="B157" t="s">
+        <v>19</v>
+      </c>
+      <c r="C157" t="s">
+        <v>20</v>
+      </c>
+      <c r="F157">
+        <v>2779318867</v>
+      </c>
+      <c r="G157" s="2">
+        <v>179085930787771</v>
+      </c>
+      <c r="H157" t="s">
+        <v>21</v>
+      </c>
+      <c r="I157" t="s">
+        <v>32</v>
+      </c>
+      <c r="J157" t="s">
+        <v>23</v>
+      </c>
+      <c r="K157" t="s">
+        <v>24</v>
+      </c>
+      <c r="L157" t="s">
+        <v>35</v>
+      </c>
+      <c r="N157" t="s">
+        <v>29</v>
+      </c>
+      <c r="O157">
+        <v>16</v>
+      </c>
+      <c r="R157" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="S157" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>46296.414942129632</v>
+      </c>
+      <c r="B158" t="s">
+        <v>19</v>
+      </c>
+      <c r="C158" t="s">
+        <v>20</v>
+      </c>
+      <c r="F158">
+        <v>2762947068</v>
+      </c>
+      <c r="G158" s="2">
+        <v>179085945190931</v>
+      </c>
+      <c r="H158" t="s">
+        <v>21</v>
+      </c>
+      <c r="I158" t="s">
+        <v>77</v>
+      </c>
+      <c r="J158" t="s">
+        <v>23</v>
+      </c>
+      <c r="K158" t="s">
+        <v>24</v>
+      </c>
+      <c r="N158" t="s">
+        <v>29</v>
+      </c>
+      <c r="O158">
+        <v>16</v>
+      </c>
+      <c r="R158" s="3">
+        <v>2.2685185185185187E-3</v>
+      </c>
+      <c r="S158" s="3">
+        <v>2.0601851851851853E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>46296.705671296295</v>
+      </c>
+      <c r="B159" t="s">
+        <v>19</v>
+      </c>
+      <c r="C159" t="s">
+        <v>20</v>
+      </c>
+      <c r="F159">
+        <v>2761341376</v>
+      </c>
+      <c r="G159" s="2">
+        <v>1790884509751290</v>
+      </c>
+      <c r="H159" t="s">
+        <v>21</v>
+      </c>
+      <c r="I159" t="s">
+        <v>79</v>
+      </c>
+      <c r="J159" t="s">
+        <v>23</v>
+      </c>
+      <c r="K159" t="s">
+        <v>37</v>
+      </c>
+      <c r="N159" t="s">
+        <v>29</v>
+      </c>
+      <c r="O159">
+        <v>19</v>
+      </c>
+      <c r="R159" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S159" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>46296.706377314818</v>
+      </c>
+      <c r="B160" t="s">
+        <v>19</v>
+      </c>
+      <c r="C160" t="s">
+        <v>20</v>
+      </c>
+      <c r="F160">
+        <v>2783160867</v>
+      </c>
+      <c r="G160" s="2">
+        <v>1790884631753200</v>
+      </c>
+      <c r="H160" t="s">
+        <v>21</v>
+      </c>
+      <c r="I160" t="s">
+        <v>81</v>
+      </c>
+      <c r="J160" t="s">
+        <v>23</v>
+      </c>
+      <c r="K160" t="s">
+        <v>24</v>
+      </c>
+      <c r="L160" t="s">
+        <v>35</v>
+      </c>
+      <c r="N160" t="s">
+        <v>25</v>
+      </c>
+      <c r="O160">
+        <v>16</v>
+      </c>
+      <c r="R160" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="S160" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>46296.715231481481</v>
+      </c>
+      <c r="B161" t="s">
+        <v>19</v>
+      </c>
+      <c r="C161" t="s">
+        <v>20</v>
+      </c>
+      <c r="F161">
+        <v>2759671820</v>
+      </c>
+      <c r="G161" s="2">
+        <v>1790885396770830</v>
+      </c>
+      <c r="H161" t="s">
+        <v>21</v>
+      </c>
+      <c r="I161" t="s">
+        <v>84</v>
+      </c>
+      <c r="J161" t="s">
+        <v>23</v>
+      </c>
+      <c r="K161" t="s">
+        <v>24</v>
+      </c>
+      <c r="N161" t="s">
+        <v>29</v>
+      </c>
+      <c r="O161">
+        <v>16</v>
+      </c>
+      <c r="R161" s="3">
+        <v>1.5856481481481481E-3</v>
+      </c>
+      <c r="S161" s="3">
+        <v>1.4120370370370369E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>46296.722280092596</v>
+      </c>
+      <c r="B162" t="s">
+        <v>19</v>
+      </c>
+      <c r="C162" t="s">
+        <v>20</v>
+      </c>
+      <c r="F162">
+        <v>2761342811</v>
+      </c>
+      <c r="G162" s="2">
+        <v>1790885944783410</v>
+      </c>
+      <c r="H162" t="s">
+        <v>21</v>
+      </c>
+      <c r="I162" t="s">
+        <v>79</v>
+      </c>
+      <c r="J162" t="s">
+        <v>23</v>
+      </c>
+      <c r="K162" t="s">
+        <v>37</v>
+      </c>
+      <c r="N162" t="s">
+        <v>29</v>
+      </c>
+      <c r="O162">
+        <v>19</v>
+      </c>
+      <c r="R162" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S162" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>46296.72384259259</v>
+      </c>
+      <c r="B163" t="s">
+        <v>19</v>
+      </c>
+      <c r="C163" t="s">
+        <v>20</v>
+      </c>
+      <c r="F163">
+        <v>2761342946</v>
+      </c>
+      <c r="G163" s="2">
+        <v>1790886079786020</v>
+      </c>
+      <c r="H163" t="s">
+        <v>21</v>
+      </c>
+      <c r="I163" t="s">
+        <v>79</v>
+      </c>
+      <c r="J163" t="s">
+        <v>23</v>
+      </c>
+      <c r="K163" t="s">
+        <v>37</v>
+      </c>
+      <c r="N163" t="s">
+        <v>29</v>
+      </c>
+      <c r="O163">
+        <v>19</v>
+      </c>
+      <c r="R163" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S163" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>46296.724479166667</v>
+      </c>
+      <c r="B164" t="s">
+        <v>19</v>
+      </c>
+      <c r="C164" t="s">
+        <v>20</v>
+      </c>
+      <c r="F164">
+        <v>2783162431</v>
+      </c>
+      <c r="G164" s="2">
+        <v>1790886195787720</v>
+      </c>
+      <c r="H164" t="s">
+        <v>21</v>
+      </c>
+      <c r="I164" t="s">
+        <v>81</v>
+      </c>
+      <c r="J164" t="s">
+        <v>23</v>
+      </c>
+      <c r="K164" t="s">
+        <v>24</v>
+      </c>
+      <c r="N164" t="s">
+        <v>25</v>
+      </c>
+      <c r="O164">
+        <v>16</v>
+      </c>
+      <c r="R164" s="3">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="S164" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>46296.725289351853</v>
+      </c>
+      <c r="B165" t="s">
+        <v>19</v>
+      </c>
+      <c r="C165" t="s">
+        <v>20</v>
+      </c>
+      <c r="F165">
+        <v>2783162501</v>
+      </c>
+      <c r="G165" s="2">
+        <v>1790886265788950</v>
+      </c>
+      <c r="H165" t="s">
+        <v>21</v>
+      </c>
+      <c r="I165" t="s">
+        <v>81</v>
+      </c>
+      <c r="J165" t="s">
+        <v>23</v>
+      </c>
+      <c r="K165" t="s">
+        <v>24</v>
+      </c>
+      <c r="N165" t="s">
+        <v>25</v>
+      </c>
+      <c r="O165">
+        <v>16</v>
+      </c>
+      <c r="R165" s="3">
+        <v>1.8287037037037037E-3</v>
+      </c>
+      <c r="S165" s="3">
+        <v>1.8055555555555555E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>46296.727152777778</v>
+      </c>
+      <c r="B166" t="s">
+        <v>19</v>
+      </c>
+      <c r="C166" t="s">
+        <v>20</v>
+      </c>
+      <c r="F166">
+        <v>2783162662</v>
+      </c>
+      <c r="G166" s="2">
+        <v>1790886426793040</v>
+      </c>
+      <c r="H166" t="s">
+        <v>21</v>
+      </c>
+      <c r="I166" t="s">
+        <v>81</v>
+      </c>
+      <c r="J166" t="s">
+        <v>23</v>
+      </c>
+      <c r="K166" t="s">
+        <v>24</v>
+      </c>
+      <c r="N166" t="s">
+        <v>25</v>
+      </c>
+      <c r="O166">
+        <v>16</v>
+      </c>
+      <c r="R166" s="3">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="S166" s="3">
+        <v>7.8703703703703705E-4</v>
       </c>
     </row>
   </sheetData>

--- a/Arquivos/nao_atualizaveis/Ativo_IMES/DISCAGEM_IMES.xlsx
+++ b/Arquivos/nao_atualizaveis/Ativo_IMES/DISCAGEM_IMES.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Ativo_IMES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CF91A7-9AD2-49A2-A28F-A831926327D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B580057-809C-4242-A2C3-BFDE844BD365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{123B1522-D3FF-4DAC-9F1A-AEADB0465F69}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{123B1522-D3FF-4DAC-9F1A-AEADB0465F69}"/>
   </bookViews>
   <sheets>
     <sheet name="chamadas_30-09-2026_134043" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'chamadas_30-09-2026_134043'!$A$1:$S$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'chamadas_30-09-2026_134043'!$A$1:$S$230</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="89">
   <si>
     <t>DATA</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Troca de Representante</t>
+  </si>
+  <si>
+    <t>99842-8835</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{100F3FCB-6525-4D20-BE0A-5478D5F6F3FE}">
-  <dimension ref="A1:S166"/>
+  <dimension ref="A1:S230"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -1141,7 +1144,7 @@
     <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
     <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="27.44140625" bestFit="1" customWidth="1"/>
@@ -1833,6 +1836,9 @@
       <c r="K16" t="s">
         <v>24</v>
       </c>
+      <c r="L16" t="s">
+        <v>85</v>
+      </c>
       <c r="N16" t="s">
         <v>29</v>
       </c>
@@ -4847,7 +4853,7 @@
         <v>24</v>
       </c>
       <c r="L87" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="N87" t="s">
         <v>25</v>
@@ -5655,6 +5661,9 @@
       <c r="K106" t="s">
         <v>37</v>
       </c>
+      <c r="L106" t="s">
+        <v>86</v>
+      </c>
       <c r="N106" t="s">
         <v>29</v>
       </c>
@@ -5828,9 +5837,6 @@
       <c r="K110" t="s">
         <v>24</v>
       </c>
-      <c r="L110" t="s">
-        <v>86</v>
-      </c>
       <c r="N110" t="s">
         <v>25</v>
       </c>
@@ -6628,6 +6634,9 @@
       <c r="K129" t="s">
         <v>37</v>
       </c>
+      <c r="L129" t="s">
+        <v>86</v>
+      </c>
       <c r="N129" t="s">
         <v>29</v>
       </c>
@@ -8000,6 +8009,9 @@
       <c r="K161" t="s">
         <v>24</v>
       </c>
+      <c r="L161" t="s">
+        <v>86</v>
+      </c>
       <c r="N161" t="s">
         <v>29</v>
       </c>
@@ -8218,7 +8230,2746 @@
         <v>7.8703703703703705E-4</v>
       </c>
     </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>46297.380590277775</v>
+      </c>
+      <c r="B167" t="s">
+        <v>19</v>
+      </c>
+      <c r="C167" t="s">
+        <v>20</v>
+      </c>
+      <c r="F167">
+        <v>2789371738</v>
+      </c>
+      <c r="G167" s="2">
+        <v>179094288264121</v>
+      </c>
+      <c r="H167" t="s">
+        <v>21</v>
+      </c>
+      <c r="I167" t="s">
+        <v>88</v>
+      </c>
+      <c r="J167" t="s">
+        <v>23</v>
+      </c>
+      <c r="K167" t="s">
+        <v>37</v>
+      </c>
+      <c r="N167" t="s">
+        <v>29</v>
+      </c>
+      <c r="O167">
+        <v>1</v>
+      </c>
+      <c r="R167" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S167" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>46297.38140046296</v>
+      </c>
+      <c r="B168" t="s">
+        <v>19</v>
+      </c>
+      <c r="C168" t="s">
+        <v>20</v>
+      </c>
+      <c r="F168">
+        <v>2789371800</v>
+      </c>
+      <c r="G168" s="2">
+        <v>179094294465821</v>
+      </c>
+      <c r="H168" t="s">
+        <v>21</v>
+      </c>
+      <c r="I168" t="s">
+        <v>88</v>
+      </c>
+      <c r="J168" t="s">
+        <v>23</v>
+      </c>
+      <c r="K168" t="s">
+        <v>28</v>
+      </c>
+      <c r="N168" t="s">
+        <v>29</v>
+      </c>
+      <c r="O168">
+        <v>17</v>
+      </c>
+      <c r="R168" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S168" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A169" s="1">
+        <v>46297.381481481483</v>
+      </c>
+      <c r="B169" t="s">
+        <v>19</v>
+      </c>
+      <c r="C169" t="s">
+        <v>20</v>
+      </c>
+      <c r="F169">
+        <v>2789371816</v>
+      </c>
+      <c r="G169" s="2">
+        <v>179094296066281</v>
+      </c>
+      <c r="H169" t="s">
+        <v>21</v>
+      </c>
+      <c r="I169" t="s">
+        <v>88</v>
+      </c>
+      <c r="J169" t="s">
+        <v>23</v>
+      </c>
+      <c r="K169" t="s">
+        <v>24</v>
+      </c>
+      <c r="L169" t="s">
+        <v>86</v>
+      </c>
+      <c r="N169" t="s">
+        <v>29</v>
+      </c>
+      <c r="O169">
+        <v>16</v>
+      </c>
+      <c r="R169" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="S169" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>46297.384942129633</v>
+      </c>
+      <c r="B170" t="s">
+        <v>19</v>
+      </c>
+      <c r="C170" t="s">
+        <v>20</v>
+      </c>
+      <c r="F170">
+        <v>2790862132</v>
+      </c>
+      <c r="G170" s="2">
+        <v>179094325972791</v>
+      </c>
+      <c r="H170" t="s">
+        <v>21</v>
+      </c>
+      <c r="I170" t="s">
+        <v>22</v>
+      </c>
+      <c r="J170" t="s">
+        <v>23</v>
+      </c>
+      <c r="K170" t="s">
+        <v>24</v>
+      </c>
+      <c r="L170" t="s">
+        <v>35</v>
+      </c>
+      <c r="N170" t="s">
+        <v>25</v>
+      </c>
+      <c r="O170">
+        <v>16</v>
+      </c>
+      <c r="R170" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S170" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>46297.385127314818</v>
+      </c>
+      <c r="B171" t="s">
+        <v>19</v>
+      </c>
+      <c r="C171" t="s">
+        <v>20</v>
+      </c>
+      <c r="F171">
+        <v>2790862148</v>
+      </c>
+      <c r="G171" s="2">
+        <v>179094327573091</v>
+      </c>
+      <c r="H171" t="s">
+        <v>21</v>
+      </c>
+      <c r="I171" t="s">
+        <v>22</v>
+      </c>
+      <c r="J171" t="s">
+        <v>23</v>
+      </c>
+      <c r="K171" t="s">
+        <v>24</v>
+      </c>
+      <c r="L171" t="s">
+        <v>35</v>
+      </c>
+      <c r="N171" t="s">
+        <v>29</v>
+      </c>
+      <c r="O171">
+        <v>16</v>
+      </c>
+      <c r="R171" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S171" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>46297.392418981479</v>
+      </c>
+      <c r="B172" t="s">
+        <v>19</v>
+      </c>
+      <c r="C172" t="s">
+        <v>20</v>
+      </c>
+      <c r="F172">
+        <v>2761400772</v>
+      </c>
+      <c r="G172" s="2">
+        <v>179094390582121</v>
+      </c>
+      <c r="H172" t="s">
+        <v>21</v>
+      </c>
+      <c r="I172" t="s">
+        <v>79</v>
+      </c>
+      <c r="J172" t="s">
+        <v>23</v>
+      </c>
+      <c r="K172" t="s">
+        <v>24</v>
+      </c>
+      <c r="L172" t="s">
+        <v>35</v>
+      </c>
+      <c r="N172" t="s">
+        <v>29</v>
+      </c>
+      <c r="O172">
+        <v>16</v>
+      </c>
+      <c r="R172" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S172" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>46297.393506944441</v>
+      </c>
+      <c r="B173" t="s">
+        <v>19</v>
+      </c>
+      <c r="C173" t="s">
+        <v>20</v>
+      </c>
+      <c r="F173">
+        <v>2783220235</v>
+      </c>
+      <c r="G173" s="2">
+        <v>179094399984271</v>
+      </c>
+      <c r="H173" t="s">
+        <v>21</v>
+      </c>
+      <c r="I173" t="s">
+        <v>81</v>
+      </c>
+      <c r="J173" t="s">
+        <v>23</v>
+      </c>
+      <c r="K173" t="s">
+        <v>24</v>
+      </c>
+      <c r="N173" t="s">
+        <v>25</v>
+      </c>
+      <c r="O173">
+        <v>16</v>
+      </c>
+      <c r="R173" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S173" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>46297.394537037035</v>
+      </c>
+      <c r="B174" t="s">
+        <v>19</v>
+      </c>
+      <c r="C174" t="s">
+        <v>20</v>
+      </c>
+      <c r="F174">
+        <v>2761400955</v>
+      </c>
+      <c r="G174" s="2">
+        <v>179094408786271</v>
+      </c>
+      <c r="H174" t="s">
+        <v>21</v>
+      </c>
+      <c r="I174" t="s">
+        <v>79</v>
+      </c>
+      <c r="J174" t="s">
+        <v>23</v>
+      </c>
+      <c r="K174" t="s">
+        <v>37</v>
+      </c>
+      <c r="N174" t="s">
+        <v>29</v>
+      </c>
+      <c r="O174">
+        <v>1</v>
+      </c>
+      <c r="R174" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S174" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>46297.396932870368</v>
+      </c>
+      <c r="B175" t="s">
+        <v>19</v>
+      </c>
+      <c r="C175" t="s">
+        <v>20</v>
+      </c>
+      <c r="F175">
+        <v>2761401162</v>
+      </c>
+      <c r="G175" s="2">
+        <v>179094429590601</v>
+      </c>
+      <c r="H175" t="s">
+        <v>21</v>
+      </c>
+      <c r="I175" t="s">
+        <v>79</v>
+      </c>
+      <c r="J175" t="s">
+        <v>23</v>
+      </c>
+      <c r="K175" t="s">
+        <v>24</v>
+      </c>
+      <c r="L175" t="s">
+        <v>35</v>
+      </c>
+      <c r="N175" t="s">
+        <v>29</v>
+      </c>
+      <c r="O175">
+        <v>16</v>
+      </c>
+      <c r="R175" s="3">
+        <v>2.2337962962962962E-3</v>
+      </c>
+      <c r="S175" s="3">
+        <v>2.1180555555555558E-3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>46297.401967592596</v>
+      </c>
+      <c r="B176" t="s">
+        <v>19</v>
+      </c>
+      <c r="C176" t="s">
+        <v>20</v>
+      </c>
+      <c r="F176">
+        <v>2761401597</v>
+      </c>
+      <c r="G176" s="2">
+        <v>1790944730104670</v>
+      </c>
+      <c r="H176" t="s">
+        <v>21</v>
+      </c>
+      <c r="I176" t="s">
+        <v>79</v>
+      </c>
+      <c r="J176" t="s">
+        <v>23</v>
+      </c>
+      <c r="K176" t="s">
+        <v>37</v>
+      </c>
+      <c r="N176" t="s">
+        <v>29</v>
+      </c>
+      <c r="O176">
+        <v>1</v>
+      </c>
+      <c r="R176" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S176" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>46297.403124999997</v>
+      </c>
+      <c r="B177" t="s">
+        <v>19</v>
+      </c>
+      <c r="C177" t="s">
+        <v>20</v>
+      </c>
+      <c r="F177">
+        <v>2761401697</v>
+      </c>
+      <c r="G177" s="2">
+        <v>1790944830107200</v>
+      </c>
+      <c r="H177" t="s">
+        <v>21</v>
+      </c>
+      <c r="I177" t="s">
+        <v>79</v>
+      </c>
+      <c r="J177" t="s">
+        <v>23</v>
+      </c>
+      <c r="K177" t="s">
+        <v>24</v>
+      </c>
+      <c r="L177" t="s">
+        <v>35</v>
+      </c>
+      <c r="N177" t="s">
+        <v>29</v>
+      </c>
+      <c r="O177">
+        <v>16</v>
+      </c>
+      <c r="R177" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="S177" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>46297.404849537037</v>
+      </c>
+      <c r="B178" t="s">
+        <v>19</v>
+      </c>
+      <c r="C178" t="s">
+        <v>20</v>
+      </c>
+      <c r="F178">
+        <v>2790860569</v>
+      </c>
+      <c r="G178" s="2">
+        <v>1790944979111730</v>
+      </c>
+      <c r="H178" t="s">
+        <v>21</v>
+      </c>
+      <c r="I178" t="s">
+        <v>33</v>
+      </c>
+      <c r="J178" t="s">
+        <v>23</v>
+      </c>
+      <c r="K178" t="s">
+        <v>24</v>
+      </c>
+      <c r="L178" t="s">
+        <v>86</v>
+      </c>
+      <c r="N178" t="s">
+        <v>29</v>
+      </c>
+      <c r="O178">
+        <v>16</v>
+      </c>
+      <c r="R178" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="S178" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>46297.406342592592</v>
+      </c>
+      <c r="B179" t="s">
+        <v>19</v>
+      </c>
+      <c r="C179" t="s">
+        <v>20</v>
+      </c>
+      <c r="F179">
+        <v>2780986140</v>
+      </c>
+      <c r="G179" s="2">
+        <v>1790945108113900</v>
+      </c>
+      <c r="H179" t="s">
+        <v>21</v>
+      </c>
+      <c r="I179" t="s">
+        <v>34</v>
+      </c>
+      <c r="J179" t="s">
+        <v>23</v>
+      </c>
+      <c r="K179" t="s">
+        <v>24</v>
+      </c>
+      <c r="L179" t="s">
+        <v>35</v>
+      </c>
+      <c r="N179" t="s">
+        <v>29</v>
+      </c>
+      <c r="O179">
+        <v>16</v>
+      </c>
+      <c r="R179" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S179" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>46297.407233796293</v>
+      </c>
+      <c r="B180" t="s">
+        <v>19</v>
+      </c>
+      <c r="C180" t="s">
+        <v>20</v>
+      </c>
+      <c r="F180">
+        <v>2780986217</v>
+      </c>
+      <c r="G180" s="2">
+        <v>1790945185114330</v>
+      </c>
+      <c r="H180" t="s">
+        <v>21</v>
+      </c>
+      <c r="I180" t="s">
+        <v>34</v>
+      </c>
+      <c r="J180" t="s">
+        <v>23</v>
+      </c>
+      <c r="K180" t="s">
+        <v>24</v>
+      </c>
+      <c r="L180" t="s">
+        <v>35</v>
+      </c>
+      <c r="N180" t="s">
+        <v>25</v>
+      </c>
+      <c r="O180">
+        <v>16</v>
+      </c>
+      <c r="R180" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S180" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A181" s="1">
+        <v>46297.407476851855</v>
+      </c>
+      <c r="B181" t="s">
+        <v>19</v>
+      </c>
+      <c r="C181" t="s">
+        <v>20</v>
+      </c>
+      <c r="F181">
+        <v>2780986238</v>
+      </c>
+      <c r="G181" s="2">
+        <v>1790945206114520</v>
+      </c>
+      <c r="H181" t="s">
+        <v>21</v>
+      </c>
+      <c r="I181" t="s">
+        <v>34</v>
+      </c>
+      <c r="J181" t="s">
+        <v>23</v>
+      </c>
+      <c r="K181" t="s">
+        <v>24</v>
+      </c>
+      <c r="L181" t="s">
+        <v>35</v>
+      </c>
+      <c r="N181" t="s">
+        <v>25</v>
+      </c>
+      <c r="O181">
+        <v>16</v>
+      </c>
+      <c r="R181" s="3">
+        <v>1.2152777777777778E-3</v>
+      </c>
+      <c r="S181" s="3">
+        <v>9.9537037037037042E-4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>46297.411886574075</v>
+      </c>
+      <c r="B182" t="s">
+        <v>19</v>
+      </c>
+      <c r="C182" t="s">
+        <v>20</v>
+      </c>
+      <c r="F182">
+        <v>2755459524</v>
+      </c>
+      <c r="G182" s="2">
+        <v>1790945587119630</v>
+      </c>
+      <c r="H182" t="s">
+        <v>21</v>
+      </c>
+      <c r="I182" t="s">
+        <v>39</v>
+      </c>
+      <c r="J182" t="s">
+        <v>23</v>
+      </c>
+      <c r="K182" t="s">
+        <v>24</v>
+      </c>
+      <c r="L182" t="s">
+        <v>35</v>
+      </c>
+      <c r="N182" t="s">
+        <v>25</v>
+      </c>
+      <c r="O182">
+        <v>16</v>
+      </c>
+      <c r="R182" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="S182" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>46297.414803240739</v>
+      </c>
+      <c r="B183" t="s">
+        <v>19</v>
+      </c>
+      <c r="C183" t="s">
+        <v>20</v>
+      </c>
+      <c r="F183">
+        <v>2772578342</v>
+      </c>
+      <c r="G183" s="2">
+        <v>1790945839122310</v>
+      </c>
+      <c r="H183" t="s">
+        <v>21</v>
+      </c>
+      <c r="I183" t="s">
+        <v>45</v>
+      </c>
+      <c r="J183" t="s">
+        <v>23</v>
+      </c>
+      <c r="K183" t="s">
+        <v>24</v>
+      </c>
+      <c r="L183" t="s">
+        <v>35</v>
+      </c>
+      <c r="N183" t="s">
+        <v>25</v>
+      </c>
+      <c r="O183">
+        <v>16</v>
+      </c>
+      <c r="R183" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="S183" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>46297.415358796294</v>
+      </c>
+      <c r="B184" t="s">
+        <v>19</v>
+      </c>
+      <c r="C184" t="s">
+        <v>20</v>
+      </c>
+      <c r="F184">
+        <v>2772578390</v>
+      </c>
+      <c r="G184" s="2">
+        <v>1790945887122960</v>
+      </c>
+      <c r="H184" t="s">
+        <v>21</v>
+      </c>
+      <c r="I184" t="s">
+        <v>45</v>
+      </c>
+      <c r="J184" t="s">
+        <v>23</v>
+      </c>
+      <c r="K184" t="s">
+        <v>24</v>
+      </c>
+      <c r="L184" t="s">
+        <v>35</v>
+      </c>
+      <c r="N184" t="s">
+        <v>29</v>
+      </c>
+      <c r="O184">
+        <v>16</v>
+      </c>
+      <c r="R184" s="3">
+        <v>1.6898148148148148E-3</v>
+      </c>
+      <c r="S184" s="3">
+        <v>1.4467592592592592E-3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>46297.418090277781</v>
+      </c>
+      <c r="B185" t="s">
+        <v>19</v>
+      </c>
+      <c r="C185" t="s">
+        <v>20</v>
+      </c>
+      <c r="F185">
+        <v>2763768349</v>
+      </c>
+      <c r="G185" s="2">
+        <v>1790946123127240</v>
+      </c>
+      <c r="H185" t="s">
+        <v>21</v>
+      </c>
+      <c r="I185" t="s">
+        <v>46</v>
+      </c>
+      <c r="J185" t="s">
+        <v>23</v>
+      </c>
+      <c r="K185" t="s">
+        <v>24</v>
+      </c>
+      <c r="L185" t="s">
+        <v>35</v>
+      </c>
+      <c r="N185" t="s">
+        <v>25</v>
+      </c>
+      <c r="O185">
+        <v>16</v>
+      </c>
+      <c r="R185" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="S185" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A186" s="1">
+        <v>46297.419629629629</v>
+      </c>
+      <c r="B186" t="s">
+        <v>19</v>
+      </c>
+      <c r="C186" t="s">
+        <v>20</v>
+      </c>
+      <c r="F186">
+        <v>2763768482</v>
+      </c>
+      <c r="G186" s="2">
+        <v>1790946256131080</v>
+      </c>
+      <c r="H186" t="s">
+        <v>21</v>
+      </c>
+      <c r="I186" t="s">
+        <v>46</v>
+      </c>
+      <c r="J186" t="s">
+        <v>23</v>
+      </c>
+      <c r="K186" t="s">
+        <v>24</v>
+      </c>
+      <c r="L186" t="s">
+        <v>35</v>
+      </c>
+      <c r="N186" t="s">
+        <v>25</v>
+      </c>
+      <c r="O186">
+        <v>16</v>
+      </c>
+      <c r="R186" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S186" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A187" s="1">
+        <v>46297.420937499999</v>
+      </c>
+      <c r="B187" t="s">
+        <v>19</v>
+      </c>
+      <c r="C187" t="s">
+        <v>20</v>
+      </c>
+      <c r="F187">
+        <v>2763768595</v>
+      </c>
+      <c r="G187" s="2">
+        <v>1790946369134730</v>
+      </c>
+      <c r="H187" t="s">
+        <v>21</v>
+      </c>
+      <c r="I187" t="s">
+        <v>46</v>
+      </c>
+      <c r="J187" t="s">
+        <v>23</v>
+      </c>
+      <c r="K187" t="s">
+        <v>24</v>
+      </c>
+      <c r="L187" t="s">
+        <v>35</v>
+      </c>
+      <c r="N187" t="s">
+        <v>29</v>
+      </c>
+      <c r="O187">
+        <v>16</v>
+      </c>
+      <c r="R187" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S187" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A188" s="1">
+        <v>46297.421805555554</v>
+      </c>
+      <c r="B188" t="s">
+        <v>19</v>
+      </c>
+      <c r="C188" t="s">
+        <v>20</v>
+      </c>
+      <c r="F188">
+        <v>2763768670</v>
+      </c>
+      <c r="G188" s="2">
+        <v>1790946444136290</v>
+      </c>
+      <c r="H188" t="s">
+        <v>21</v>
+      </c>
+      <c r="I188" t="s">
+        <v>46</v>
+      </c>
+      <c r="J188" t="s">
+        <v>23</v>
+      </c>
+      <c r="K188" t="s">
+        <v>24</v>
+      </c>
+      <c r="L188" t="s">
+        <v>35</v>
+      </c>
+      <c r="N188" t="s">
+        <v>29</v>
+      </c>
+      <c r="O188">
+        <v>16</v>
+      </c>
+      <c r="R188" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="S188" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A189" s="1">
+        <v>46297.422951388886</v>
+      </c>
+      <c r="B189" t="s">
+        <v>19</v>
+      </c>
+      <c r="C189" t="s">
+        <v>20</v>
+      </c>
+      <c r="F189">
+        <v>2763768769</v>
+      </c>
+      <c r="G189" s="2">
+        <v>1790946543137770</v>
+      </c>
+      <c r="H189" t="s">
+        <v>21</v>
+      </c>
+      <c r="I189" t="s">
+        <v>46</v>
+      </c>
+      <c r="J189" t="s">
+        <v>23</v>
+      </c>
+      <c r="K189" t="s">
+        <v>24</v>
+      </c>
+      <c r="L189" t="s">
+        <v>85</v>
+      </c>
+      <c r="N189" t="s">
+        <v>29</v>
+      </c>
+      <c r="O189">
+        <v>16</v>
+      </c>
+      <c r="R189" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S189" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A190" s="1">
+        <v>46297.425185185188</v>
+      </c>
+      <c r="B190" t="s">
+        <v>19</v>
+      </c>
+      <c r="C190" t="s">
+        <v>20</v>
+      </c>
+      <c r="F190">
+        <v>2761403543</v>
+      </c>
+      <c r="G190" s="2">
+        <v>1790946676142050</v>
+      </c>
+      <c r="H190" t="s">
+        <v>21</v>
+      </c>
+      <c r="I190" t="s">
+        <v>79</v>
+      </c>
+      <c r="J190" t="s">
+        <v>23</v>
+      </c>
+      <c r="K190" t="s">
+        <v>37</v>
+      </c>
+      <c r="N190" t="s">
+        <v>29</v>
+      </c>
+      <c r="O190">
+        <v>19</v>
+      </c>
+      <c r="R190" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S190" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A191" s="1">
+        <v>46297.42591435185</v>
+      </c>
+      <c r="B191" t="s">
+        <v>19</v>
+      </c>
+      <c r="C191" t="s">
+        <v>20</v>
+      </c>
+      <c r="F191">
+        <v>2783223035</v>
+      </c>
+      <c r="G191" s="2">
+        <v>1790946799144140</v>
+      </c>
+      <c r="H191" t="s">
+        <v>21</v>
+      </c>
+      <c r="I191" t="s">
+        <v>81</v>
+      </c>
+      <c r="J191" t="s">
+        <v>23</v>
+      </c>
+      <c r="K191" t="s">
+        <v>24</v>
+      </c>
+      <c r="L191" t="s">
+        <v>35</v>
+      </c>
+      <c r="N191" t="s">
+        <v>25</v>
+      </c>
+      <c r="O191">
+        <v>16</v>
+      </c>
+      <c r="R191" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S191" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A192" s="1">
+        <v>46297.42628472222</v>
+      </c>
+      <c r="B192" t="s">
+        <v>19</v>
+      </c>
+      <c r="C192" t="s">
+        <v>20</v>
+      </c>
+      <c r="F192">
+        <v>2761403698</v>
+      </c>
+      <c r="G192" s="2">
+        <v>1790946831144780</v>
+      </c>
+      <c r="H192" t="s">
+        <v>21</v>
+      </c>
+      <c r="I192" t="s">
+        <v>79</v>
+      </c>
+      <c r="J192" t="s">
+        <v>23</v>
+      </c>
+      <c r="K192" t="s">
+        <v>24</v>
+      </c>
+      <c r="L192" t="s">
+        <v>35</v>
+      </c>
+      <c r="N192" t="s">
+        <v>29</v>
+      </c>
+      <c r="O192">
+        <v>16</v>
+      </c>
+      <c r="R192" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="S192" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A193" s="1">
+        <v>46297.427291666667</v>
+      </c>
+      <c r="B193" t="s">
+        <v>19</v>
+      </c>
+      <c r="C193" t="s">
+        <v>20</v>
+      </c>
+      <c r="F193">
+        <v>2785217788</v>
+      </c>
+      <c r="G193" s="2">
+        <v>1790946918146160</v>
+      </c>
+      <c r="H193" t="s">
+        <v>21</v>
+      </c>
+      <c r="I193" t="s">
+        <v>47</v>
+      </c>
+      <c r="J193" t="s">
+        <v>23</v>
+      </c>
+      <c r="K193" t="s">
+        <v>24</v>
+      </c>
+      <c r="L193" t="s">
+        <v>86</v>
+      </c>
+      <c r="N193" t="s">
+        <v>29</v>
+      </c>
+      <c r="O193">
+        <v>16</v>
+      </c>
+      <c r="R193" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="S193" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A194" s="1">
+        <v>46297.430104166669</v>
+      </c>
+      <c r="B194" t="s">
+        <v>19</v>
+      </c>
+      <c r="C194" t="s">
+        <v>20</v>
+      </c>
+      <c r="F194">
+        <v>2771997847</v>
+      </c>
+      <c r="G194" s="2">
+        <v>1790947161150450</v>
+      </c>
+      <c r="H194" t="s">
+        <v>21</v>
+      </c>
+      <c r="I194" t="s">
+        <v>48</v>
+      </c>
+      <c r="J194" t="s">
+        <v>23</v>
+      </c>
+      <c r="K194" t="s">
+        <v>24</v>
+      </c>
+      <c r="L194" t="s">
+        <v>35</v>
+      </c>
+      <c r="N194" t="s">
+        <v>25</v>
+      </c>
+      <c r="O194">
+        <v>16</v>
+      </c>
+      <c r="R194" s="3">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="S194" s="3">
+        <v>6.7129629629629625E-4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A195" s="1">
+        <v>46297.432071759256</v>
+      </c>
+      <c r="B195" t="s">
+        <v>19</v>
+      </c>
+      <c r="C195" t="s">
+        <v>20</v>
+      </c>
+      <c r="F195">
+        <v>2771998017</v>
+      </c>
+      <c r="G195" s="2">
+        <v>1790947331153510</v>
+      </c>
+      <c r="H195" t="s">
+        <v>21</v>
+      </c>
+      <c r="I195" t="s">
+        <v>48</v>
+      </c>
+      <c r="J195" t="s">
+        <v>23</v>
+      </c>
+      <c r="K195" t="s">
+        <v>24</v>
+      </c>
+      <c r="L195" t="s">
+        <v>35</v>
+      </c>
+      <c r="N195" t="s">
+        <v>25</v>
+      </c>
+      <c r="O195">
+        <v>16</v>
+      </c>
+      <c r="R195" s="3">
+        <v>1.3310185185185185E-3</v>
+      </c>
+      <c r="S195" s="3">
+        <v>1.2962962962962963E-3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A196" s="1">
+        <v>46297.433472222219</v>
+      </c>
+      <c r="B196" t="s">
+        <v>19</v>
+      </c>
+      <c r="C196" t="s">
+        <v>20</v>
+      </c>
+      <c r="F196">
+        <v>2788419447</v>
+      </c>
+      <c r="G196" s="2">
+        <v>1790947451156500</v>
+      </c>
+      <c r="H196" t="s">
+        <v>21</v>
+      </c>
+      <c r="I196" t="s">
+        <v>49</v>
+      </c>
+      <c r="J196" t="s">
+        <v>23</v>
+      </c>
+      <c r="K196" t="s">
+        <v>37</v>
+      </c>
+      <c r="N196" t="s">
+        <v>29</v>
+      </c>
+      <c r="O196">
+        <v>1</v>
+      </c>
+      <c r="R196" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S196" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>46297.434490740743</v>
+      </c>
+      <c r="B197" t="s">
+        <v>19</v>
+      </c>
+      <c r="C197" t="s">
+        <v>20</v>
+      </c>
+      <c r="F197">
+        <v>2788419475</v>
+      </c>
+      <c r="G197" s="2">
+        <v>1790947479157130</v>
+      </c>
+      <c r="H197" t="s">
+        <v>21</v>
+      </c>
+      <c r="I197" t="s">
+        <v>49</v>
+      </c>
+      <c r="J197" t="s">
+        <v>23</v>
+      </c>
+      <c r="K197" t="s">
+        <v>37</v>
+      </c>
+      <c r="N197" t="s">
+        <v>29</v>
+      </c>
+      <c r="O197">
+        <v>19</v>
+      </c>
+      <c r="R197" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S197" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A198" s="1">
+        <v>46297.438055555554</v>
+      </c>
+      <c r="B198" t="s">
+        <v>19</v>
+      </c>
+      <c r="C198" t="s">
+        <v>20</v>
+      </c>
+      <c r="F198">
+        <v>2788419843</v>
+      </c>
+      <c r="G198" s="2">
+        <v>1790947847167330</v>
+      </c>
+      <c r="H198" t="s">
+        <v>21</v>
+      </c>
+      <c r="I198" t="s">
+        <v>49</v>
+      </c>
+      <c r="J198" t="s">
+        <v>23</v>
+      </c>
+      <c r="K198" t="s">
+        <v>37</v>
+      </c>
+      <c r="N198" t="s">
+        <v>29</v>
+      </c>
+      <c r="O198">
+        <v>1</v>
+      </c>
+      <c r="R198" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S198" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>46297.438981481479</v>
+      </c>
+      <c r="B199" t="s">
+        <v>19</v>
+      </c>
+      <c r="C199" t="s">
+        <v>20</v>
+      </c>
+      <c r="F199">
+        <v>2784635537</v>
+      </c>
+      <c r="G199" s="2">
+        <v>1790947916169480</v>
+      </c>
+      <c r="H199" t="s">
+        <v>21</v>
+      </c>
+      <c r="I199" t="s">
+        <v>52</v>
+      </c>
+      <c r="J199" t="s">
+        <v>23</v>
+      </c>
+      <c r="K199" t="s">
+        <v>28</v>
+      </c>
+      <c r="N199" t="s">
+        <v>29</v>
+      </c>
+      <c r="O199">
+        <v>17</v>
+      </c>
+      <c r="R199" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S199" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>46297.439282407409</v>
+      </c>
+      <c r="B200" t="s">
+        <v>19</v>
+      </c>
+      <c r="C200" t="s">
+        <v>20</v>
+      </c>
+      <c r="F200">
+        <v>2784635562</v>
+      </c>
+      <c r="G200" s="2">
+        <v>1790947941170060</v>
+      </c>
+      <c r="H200" t="s">
+        <v>21</v>
+      </c>
+      <c r="I200" t="s">
+        <v>52</v>
+      </c>
+      <c r="J200" t="s">
+        <v>23</v>
+      </c>
+      <c r="K200" t="s">
+        <v>28</v>
+      </c>
+      <c r="N200" t="s">
+        <v>29</v>
+      </c>
+      <c r="O200">
+        <v>17</v>
+      </c>
+      <c r="R200" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S200" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>46297.440625000003</v>
+      </c>
+      <c r="B201" t="s">
+        <v>19</v>
+      </c>
+      <c r="C201" t="s">
+        <v>20</v>
+      </c>
+      <c r="F201">
+        <v>2762681547</v>
+      </c>
+      <c r="G201" s="2">
+        <v>1790948070173470</v>
+      </c>
+      <c r="H201" t="s">
+        <v>21</v>
+      </c>
+      <c r="I201" t="s">
+        <v>53</v>
+      </c>
+      <c r="J201" t="s">
+        <v>23</v>
+      </c>
+      <c r="K201" t="s">
+        <v>24</v>
+      </c>
+      <c r="L201" t="s">
+        <v>35</v>
+      </c>
+      <c r="N201" t="s">
+        <v>29</v>
+      </c>
+      <c r="O201">
+        <v>16</v>
+      </c>
+      <c r="R201" s="3">
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="S201" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A202" s="1">
+        <v>46297.442442129628</v>
+      </c>
+      <c r="B202" t="s">
+        <v>19</v>
+      </c>
+      <c r="C202" t="s">
+        <v>20</v>
+      </c>
+      <c r="F202">
+        <v>2762681704</v>
+      </c>
+      <c r="G202" s="2">
+        <v>1790948227176430</v>
+      </c>
+      <c r="H202" t="s">
+        <v>21</v>
+      </c>
+      <c r="I202" t="s">
+        <v>53</v>
+      </c>
+      <c r="J202" t="s">
+        <v>23</v>
+      </c>
+      <c r="K202" t="s">
+        <v>24</v>
+      </c>
+      <c r="L202" t="s">
+        <v>35</v>
+      </c>
+      <c r="N202" t="s">
+        <v>29</v>
+      </c>
+      <c r="O202">
+        <v>16</v>
+      </c>
+      <c r="R202" s="3">
+        <v>7.8703703703703705E-4</v>
+      </c>
+      <c r="S202" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>46297.444074074076</v>
+      </c>
+      <c r="B203" t="s">
+        <v>19</v>
+      </c>
+      <c r="C203" t="s">
+        <v>20</v>
+      </c>
+      <c r="F203">
+        <v>2763148522</v>
+      </c>
+      <c r="G203" s="2">
+        <v>1790948368179590</v>
+      </c>
+      <c r="H203" t="s">
+        <v>21</v>
+      </c>
+      <c r="I203" t="s">
+        <v>57</v>
+      </c>
+      <c r="J203" t="s">
+        <v>23</v>
+      </c>
+      <c r="K203" t="s">
+        <v>37</v>
+      </c>
+      <c r="N203" t="s">
+        <v>29</v>
+      </c>
+      <c r="O203">
+        <v>1</v>
+      </c>
+      <c r="R203" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S203" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A204" s="1">
+        <v>46297.444155092591</v>
+      </c>
+      <c r="B204" t="s">
+        <v>19</v>
+      </c>
+      <c r="C204" t="s">
+        <v>20</v>
+      </c>
+      <c r="F204">
+        <v>2763148528</v>
+      </c>
+      <c r="G204" s="2">
+        <v>1790948374179810</v>
+      </c>
+      <c r="H204" t="s">
+        <v>21</v>
+      </c>
+      <c r="I204" t="s">
+        <v>57</v>
+      </c>
+      <c r="J204" t="s">
+        <v>23</v>
+      </c>
+      <c r="K204" t="s">
+        <v>37</v>
+      </c>
+      <c r="N204" t="s">
+        <v>29</v>
+      </c>
+      <c r="O204">
+        <v>1</v>
+      </c>
+      <c r="R204" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S204" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A205" s="1">
+        <v>46297.44431712963</v>
+      </c>
+      <c r="B205" t="s">
+        <v>19</v>
+      </c>
+      <c r="C205" t="s">
+        <v>20</v>
+      </c>
+      <c r="F205">
+        <v>2763148542</v>
+      </c>
+      <c r="G205" s="2">
+        <v>1790948388180410</v>
+      </c>
+      <c r="H205" t="s">
+        <v>21</v>
+      </c>
+      <c r="I205" t="s">
+        <v>57</v>
+      </c>
+      <c r="J205" t="s">
+        <v>23</v>
+      </c>
+      <c r="K205" t="s">
+        <v>37</v>
+      </c>
+      <c r="N205" t="s">
+        <v>29</v>
+      </c>
+      <c r="O205">
+        <v>1</v>
+      </c>
+      <c r="R205" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S205" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A206" s="1">
+        <v>46297.452245370368</v>
+      </c>
+      <c r="B206" t="s">
+        <v>19</v>
+      </c>
+      <c r="C206" t="s">
+        <v>20</v>
+      </c>
+      <c r="F206">
+        <v>2763149227</v>
+      </c>
+      <c r="G206" s="2">
+        <v>1790949073196040</v>
+      </c>
+      <c r="H206" t="s">
+        <v>21</v>
+      </c>
+      <c r="I206" t="s">
+        <v>57</v>
+      </c>
+      <c r="J206" t="s">
+        <v>23</v>
+      </c>
+      <c r="K206" t="s">
+        <v>37</v>
+      </c>
+      <c r="N206" t="s">
+        <v>29</v>
+      </c>
+      <c r="O206">
+        <v>1</v>
+      </c>
+      <c r="R206" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S206" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A207" s="1">
+        <v>46297.452997685185</v>
+      </c>
+      <c r="B207" t="s">
+        <v>19</v>
+      </c>
+      <c r="C207" t="s">
+        <v>20</v>
+      </c>
+      <c r="F207">
+        <v>2763149293</v>
+      </c>
+      <c r="G207" s="2">
+        <v>1790949139197720</v>
+      </c>
+      <c r="H207" t="s">
+        <v>21</v>
+      </c>
+      <c r="I207" t="s">
+        <v>57</v>
+      </c>
+      <c r="J207" t="s">
+        <v>23</v>
+      </c>
+      <c r="K207" t="s">
+        <v>37</v>
+      </c>
+      <c r="N207" t="s">
+        <v>29</v>
+      </c>
+      <c r="O207">
+        <v>1</v>
+      </c>
+      <c r="R207" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S207" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A208" s="1">
+        <v>46297.453819444447</v>
+      </c>
+      <c r="B208" t="s">
+        <v>19</v>
+      </c>
+      <c r="C208" t="s">
+        <v>20</v>
+      </c>
+      <c r="F208">
+        <v>2783461993</v>
+      </c>
+      <c r="G208" s="2">
+        <v>1790949210200020</v>
+      </c>
+      <c r="H208" t="s">
+        <v>21</v>
+      </c>
+      <c r="I208" t="s">
+        <v>59</v>
+      </c>
+      <c r="J208" t="s">
+        <v>23</v>
+      </c>
+      <c r="K208" t="s">
+        <v>24</v>
+      </c>
+      <c r="L208" t="s">
+        <v>35</v>
+      </c>
+      <c r="N208" t="s">
+        <v>25</v>
+      </c>
+      <c r="O208">
+        <v>16</v>
+      </c>
+      <c r="R208" s="3">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="S208" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A209" s="1">
+        <v>46297.454768518517</v>
+      </c>
+      <c r="B209" t="s">
+        <v>19</v>
+      </c>
+      <c r="C209" t="s">
+        <v>20</v>
+      </c>
+      <c r="F209">
+        <v>2761918665</v>
+      </c>
+      <c r="G209" s="2">
+        <v>1790949292202220</v>
+      </c>
+      <c r="H209" t="s">
+        <v>21</v>
+      </c>
+      <c r="I209" t="s">
+        <v>61</v>
+      </c>
+      <c r="J209" t="s">
+        <v>23</v>
+      </c>
+      <c r="K209" t="s">
+        <v>24</v>
+      </c>
+      <c r="L209" t="s">
+        <v>35</v>
+      </c>
+      <c r="N209" t="s">
+        <v>25</v>
+      </c>
+      <c r="O209">
+        <v>16</v>
+      </c>
+      <c r="R209" s="3">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="S209" s="3">
+        <v>1.2152777777777778E-3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A210" s="1">
+        <v>46297.456921296296</v>
+      </c>
+      <c r="B210" t="s">
+        <v>19</v>
+      </c>
+      <c r="C210" t="s">
+        <v>20</v>
+      </c>
+      <c r="F210">
+        <v>2782399223</v>
+      </c>
+      <c r="G210" s="2">
+        <v>1790949478206590</v>
+      </c>
+      <c r="H210" t="s">
+        <v>21</v>
+      </c>
+      <c r="I210" t="s">
+        <v>63</v>
+      </c>
+      <c r="J210" t="s">
+        <v>23</v>
+      </c>
+      <c r="K210" t="s">
+        <v>24</v>
+      </c>
+      <c r="L210" t="s">
+        <v>35</v>
+      </c>
+      <c r="N210" t="s">
+        <v>25</v>
+      </c>
+      <c r="O210">
+        <v>16</v>
+      </c>
+      <c r="R210" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S210" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A211" s="1">
+        <v>46297.457256944443</v>
+      </c>
+      <c r="B211" t="s">
+        <v>19</v>
+      </c>
+      <c r="C211" t="s">
+        <v>20</v>
+      </c>
+      <c r="F211">
+        <v>2782399252</v>
+      </c>
+      <c r="G211" s="2">
+        <v>1790949507208060</v>
+      </c>
+      <c r="H211" t="s">
+        <v>21</v>
+      </c>
+      <c r="I211" t="s">
+        <v>63</v>
+      </c>
+      <c r="J211" t="s">
+        <v>23</v>
+      </c>
+      <c r="K211" t="s">
+        <v>24</v>
+      </c>
+      <c r="L211" t="s">
+        <v>35</v>
+      </c>
+      <c r="N211" t="s">
+        <v>25</v>
+      </c>
+      <c r="O211">
+        <v>16</v>
+      </c>
+      <c r="R211" s="3">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="S211" s="3">
+        <v>1.3541666666666667E-3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A212" s="1">
+        <v>46297.458796296298</v>
+      </c>
+      <c r="B212" t="s">
+        <v>19</v>
+      </c>
+      <c r="C212" t="s">
+        <v>20</v>
+      </c>
+      <c r="F212">
+        <v>2761406507</v>
+      </c>
+      <c r="G212" s="2">
+        <v>1790949640210870</v>
+      </c>
+      <c r="H212" t="s">
+        <v>21</v>
+      </c>
+      <c r="I212" t="s">
+        <v>79</v>
+      </c>
+      <c r="J212" t="s">
+        <v>23</v>
+      </c>
+      <c r="K212" t="s">
+        <v>24</v>
+      </c>
+      <c r="L212" t="s">
+        <v>35</v>
+      </c>
+      <c r="N212" t="s">
+        <v>25</v>
+      </c>
+      <c r="O212">
+        <v>16</v>
+      </c>
+      <c r="R212" s="3">
+        <v>1.5277777777777779E-3</v>
+      </c>
+      <c r="S212" s="3">
+        <v>1.4004629629629629E-3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A213" s="1">
+        <v>46297.460381944446</v>
+      </c>
+      <c r="B213" t="s">
+        <v>19</v>
+      </c>
+      <c r="C213" t="s">
+        <v>20</v>
+      </c>
+      <c r="F213">
+        <v>2783226013</v>
+      </c>
+      <c r="G213" s="2">
+        <v>1790949777214400</v>
+      </c>
+      <c r="H213" t="s">
+        <v>21</v>
+      </c>
+      <c r="I213" t="s">
+        <v>81</v>
+      </c>
+      <c r="J213" t="s">
+        <v>23</v>
+      </c>
+      <c r="K213" t="s">
+        <v>24</v>
+      </c>
+      <c r="L213" t="s">
+        <v>35</v>
+      </c>
+      <c r="N213" t="s">
+        <v>29</v>
+      </c>
+      <c r="O213">
+        <v>16</v>
+      </c>
+      <c r="R213" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="S213" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A214" s="1">
+        <v>46297.461608796293</v>
+      </c>
+      <c r="B214" t="s">
+        <v>19</v>
+      </c>
+      <c r="C214" t="s">
+        <v>20</v>
+      </c>
+      <c r="F214">
+        <v>2783072682</v>
+      </c>
+      <c r="G214" s="2">
+        <v>1790949823215370</v>
+      </c>
+      <c r="H214" t="s">
+        <v>21</v>
+      </c>
+      <c r="I214" t="s">
+        <v>68</v>
+      </c>
+      <c r="J214" t="s">
+        <v>23</v>
+      </c>
+      <c r="K214" t="s">
+        <v>37</v>
+      </c>
+      <c r="N214" t="s">
+        <v>29</v>
+      </c>
+      <c r="O214">
+        <v>19</v>
+      </c>
+      <c r="R214" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S214" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>46297.463819444441</v>
+      </c>
+      <c r="B215" t="s">
+        <v>19</v>
+      </c>
+      <c r="C215" t="s">
+        <v>20</v>
+      </c>
+      <c r="F215">
+        <v>2788854609</v>
+      </c>
+      <c r="G215" s="2">
+        <v>1790950048220550</v>
+      </c>
+      <c r="H215" t="s">
+        <v>21</v>
+      </c>
+      <c r="I215" t="s">
+        <v>69</v>
+      </c>
+      <c r="J215" t="s">
+        <v>23</v>
+      </c>
+      <c r="K215" t="s">
+        <v>28</v>
+      </c>
+      <c r="N215" t="s">
+        <v>29</v>
+      </c>
+      <c r="O215">
+        <v>19</v>
+      </c>
+      <c r="R215" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S215" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A216" s="1">
+        <v>46297.464525462965</v>
+      </c>
+      <c r="B216" t="s">
+        <v>19</v>
+      </c>
+      <c r="C216" t="s">
+        <v>20</v>
+      </c>
+      <c r="F216">
+        <v>2788854696</v>
+      </c>
+      <c r="G216" s="2">
+        <v>1790950135221820</v>
+      </c>
+      <c r="H216" t="s">
+        <v>21</v>
+      </c>
+      <c r="I216" t="s">
+        <v>69</v>
+      </c>
+      <c r="J216" t="s">
+        <v>23</v>
+      </c>
+      <c r="K216" t="s">
+        <v>24</v>
+      </c>
+      <c r="L216" t="s">
+        <v>35</v>
+      </c>
+      <c r="N216" t="s">
+        <v>25</v>
+      </c>
+      <c r="O216">
+        <v>16</v>
+      </c>
+      <c r="R216" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S216" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A217" s="1">
+        <v>46297.466226851851</v>
+      </c>
+      <c r="B217" t="s">
+        <v>19</v>
+      </c>
+      <c r="C217" t="s">
+        <v>20</v>
+      </c>
+      <c r="F217">
+        <v>2762280700</v>
+      </c>
+      <c r="G217" s="2">
+        <v>1790950222223770</v>
+      </c>
+      <c r="H217" t="s">
+        <v>21</v>
+      </c>
+      <c r="I217" t="s">
+        <v>70</v>
+      </c>
+      <c r="J217" t="s">
+        <v>23</v>
+      </c>
+      <c r="K217" t="s">
+        <v>37</v>
+      </c>
+      <c r="N217" t="s">
+        <v>29</v>
+      </c>
+      <c r="O217">
+        <v>19</v>
+      </c>
+      <c r="R217" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S217" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A218" s="1">
+        <v>46297.466956018521</v>
+      </c>
+      <c r="B218" t="s">
+        <v>19</v>
+      </c>
+      <c r="C218" t="s">
+        <v>20</v>
+      </c>
+      <c r="F218">
+        <v>2772662508</v>
+      </c>
+      <c r="G218" s="2">
+        <v>1790950344226530</v>
+      </c>
+      <c r="H218" t="s">
+        <v>21</v>
+      </c>
+      <c r="I218" t="s">
+        <v>71</v>
+      </c>
+      <c r="J218" t="s">
+        <v>23</v>
+      </c>
+      <c r="K218" t="s">
+        <v>37</v>
+      </c>
+      <c r="N218" t="s">
+        <v>29</v>
+      </c>
+      <c r="O218">
+        <v>1</v>
+      </c>
+      <c r="R218" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S218" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A219" s="1">
+        <v>46297.467673611114</v>
+      </c>
+      <c r="B219" t="s">
+        <v>19</v>
+      </c>
+      <c r="C219" t="s">
+        <v>20</v>
+      </c>
+      <c r="F219">
+        <v>2772662571</v>
+      </c>
+      <c r="G219" s="2">
+        <v>1790950407227470</v>
+      </c>
+      <c r="H219" t="s">
+        <v>21</v>
+      </c>
+      <c r="I219" t="s">
+        <v>71</v>
+      </c>
+      <c r="J219" t="s">
+        <v>23</v>
+      </c>
+      <c r="K219" t="s">
+        <v>24</v>
+      </c>
+      <c r="L219" t="s">
+        <v>86</v>
+      </c>
+      <c r="N219" t="s">
+        <v>29</v>
+      </c>
+      <c r="O219">
+        <v>16</v>
+      </c>
+      <c r="R219" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="S219" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A220" s="1">
+        <v>46297.47</v>
+      </c>
+      <c r="B220" t="s">
+        <v>19</v>
+      </c>
+      <c r="C220" t="s">
+        <v>20</v>
+      </c>
+      <c r="F220">
+        <v>2790946576</v>
+      </c>
+      <c r="G220" s="2">
+        <v>1790950608232280</v>
+      </c>
+      <c r="H220" t="s">
+        <v>21</v>
+      </c>
+      <c r="I220" t="s">
+        <v>73</v>
+      </c>
+      <c r="J220" t="s">
+        <v>23</v>
+      </c>
+      <c r="K220" t="s">
+        <v>24</v>
+      </c>
+      <c r="L220" t="s">
+        <v>86</v>
+      </c>
+      <c r="N220" t="s">
+        <v>25</v>
+      </c>
+      <c r="O220">
+        <v>16</v>
+      </c>
+      <c r="R220" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S220" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A221" s="1">
+        <v>46297.470983796295</v>
+      </c>
+      <c r="B221" t="s">
+        <v>19</v>
+      </c>
+      <c r="C221" t="s">
+        <v>20</v>
+      </c>
+      <c r="F221">
+        <v>2790946661</v>
+      </c>
+      <c r="G221" s="2">
+        <v>1790950693234340</v>
+      </c>
+      <c r="H221" t="s">
+        <v>21</v>
+      </c>
+      <c r="I221" t="s">
+        <v>73</v>
+      </c>
+      <c r="J221" t="s">
+        <v>23</v>
+      </c>
+      <c r="K221" t="s">
+        <v>24</v>
+      </c>
+      <c r="L221" t="s">
+        <v>35</v>
+      </c>
+      <c r="N221" t="s">
+        <v>29</v>
+      </c>
+      <c r="O221">
+        <v>16</v>
+      </c>
+      <c r="R221" s="3">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="S221" s="3">
+        <v>6.7129629629629625E-4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A222" s="1">
+        <v>46297.473298611112</v>
+      </c>
+      <c r="B222" t="s">
+        <v>19</v>
+      </c>
+      <c r="C222" t="s">
+        <v>20</v>
+      </c>
+      <c r="F222">
+        <v>2789832867</v>
+      </c>
+      <c r="G222" s="2">
+        <v>1790950892242730</v>
+      </c>
+      <c r="H222" t="s">
+        <v>21</v>
+      </c>
+      <c r="I222" t="s">
+        <v>75</v>
+      </c>
+      <c r="J222" t="s">
+        <v>23</v>
+      </c>
+      <c r="K222" t="s">
+        <v>37</v>
+      </c>
+      <c r="N222" t="s">
+        <v>29</v>
+      </c>
+      <c r="O222">
+        <v>1</v>
+      </c>
+      <c r="R222" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S222" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A223" s="1">
+        <v>46297.474652777775</v>
+      </c>
+      <c r="B223" t="s">
+        <v>19</v>
+      </c>
+      <c r="C223" t="s">
+        <v>20</v>
+      </c>
+      <c r="F223">
+        <v>2789832923</v>
+      </c>
+      <c r="G223" s="2">
+        <v>1790950949245090</v>
+      </c>
+      <c r="H223" t="s">
+        <v>21</v>
+      </c>
+      <c r="I223" t="s">
+        <v>75</v>
+      </c>
+      <c r="J223" t="s">
+        <v>23</v>
+      </c>
+      <c r="K223" t="s">
+        <v>37</v>
+      </c>
+      <c r="N223" t="s">
+        <v>29</v>
+      </c>
+      <c r="O223">
+        <v>19</v>
+      </c>
+      <c r="R223" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S223" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A224" s="1">
+        <v>46297.476111111115</v>
+      </c>
+      <c r="B224" t="s">
+        <v>19</v>
+      </c>
+      <c r="C224" t="s">
+        <v>20</v>
+      </c>
+      <c r="F224">
+        <v>2789833049</v>
+      </c>
+      <c r="G224" s="2">
+        <v>1790951075252010</v>
+      </c>
+      <c r="H224" t="s">
+        <v>21</v>
+      </c>
+      <c r="I224" t="s">
+        <v>75</v>
+      </c>
+      <c r="J224" t="s">
+        <v>23</v>
+      </c>
+      <c r="K224" t="s">
+        <v>37</v>
+      </c>
+      <c r="N224" t="s">
+        <v>29</v>
+      </c>
+      <c r="O224">
+        <v>19</v>
+      </c>
+      <c r="R224" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S224" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="225" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A225" s="1">
+        <v>46297.476898148147</v>
+      </c>
+      <c r="B225" t="s">
+        <v>19</v>
+      </c>
+      <c r="C225" t="s">
+        <v>20</v>
+      </c>
+      <c r="F225">
+        <v>2772484507</v>
+      </c>
+      <c r="G225" s="2">
+        <v>1790951204258810</v>
+      </c>
+      <c r="H225" t="s">
+        <v>21</v>
+      </c>
+      <c r="I225" t="s">
+        <v>76</v>
+      </c>
+      <c r="J225" t="s">
+        <v>23</v>
+      </c>
+      <c r="K225" t="s">
+        <v>24</v>
+      </c>
+      <c r="L225" t="s">
+        <v>35</v>
+      </c>
+      <c r="N225" t="s">
+        <v>25</v>
+      </c>
+      <c r="O225">
+        <v>16</v>
+      </c>
+      <c r="R225" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S225" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A226" s="1">
+        <v>46297.477986111109</v>
+      </c>
+      <c r="B226" t="s">
+        <v>19</v>
+      </c>
+      <c r="C226" t="s">
+        <v>20</v>
+      </c>
+      <c r="F226">
+        <v>2772484601</v>
+      </c>
+      <c r="G226" s="2">
+        <v>1790951298262890</v>
+      </c>
+      <c r="H226" t="s">
+        <v>21</v>
+      </c>
+      <c r="I226" t="s">
+        <v>76</v>
+      </c>
+      <c r="J226" t="s">
+        <v>23</v>
+      </c>
+      <c r="K226" t="s">
+        <v>24</v>
+      </c>
+      <c r="L226" t="s">
+        <v>35</v>
+      </c>
+      <c r="N226" t="s">
+        <v>25</v>
+      </c>
+      <c r="O226">
+        <v>16</v>
+      </c>
+      <c r="R226" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S226" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A227" s="1">
+        <v>46297.478993055556</v>
+      </c>
+      <c r="B227" t="s">
+        <v>19</v>
+      </c>
+      <c r="C227" t="s">
+        <v>20</v>
+      </c>
+      <c r="F227">
+        <v>2790373891</v>
+      </c>
+      <c r="G227" s="2">
+        <v>1790951385267200</v>
+      </c>
+      <c r="H227" t="s">
+        <v>21</v>
+      </c>
+      <c r="I227" t="s">
+        <v>27</v>
+      </c>
+      <c r="J227" t="s">
+        <v>23</v>
+      </c>
+      <c r="K227" t="s">
+        <v>37</v>
+      </c>
+      <c r="N227" t="s">
+        <v>25</v>
+      </c>
+      <c r="O227">
+        <v>19</v>
+      </c>
+      <c r="R227" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S227" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="228" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A228" s="1">
+        <v>46297.479826388888</v>
+      </c>
+      <c r="B228" t="s">
+        <v>19</v>
+      </c>
+      <c r="C228" t="s">
+        <v>20</v>
+      </c>
+      <c r="F228">
+        <v>2777795966</v>
+      </c>
+      <c r="G228" s="2">
+        <v>1790951457268810</v>
+      </c>
+      <c r="H228" t="s">
+        <v>21</v>
+      </c>
+      <c r="I228" t="s">
+        <v>31</v>
+      </c>
+      <c r="J228" t="s">
+        <v>23</v>
+      </c>
+      <c r="K228" t="s">
+        <v>37</v>
+      </c>
+      <c r="N228" t="s">
+        <v>25</v>
+      </c>
+      <c r="O228">
+        <v>19</v>
+      </c>
+      <c r="R228" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S228" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="229" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A229" s="1">
+        <v>46297.481296296297</v>
+      </c>
+      <c r="B229" t="s">
+        <v>19</v>
+      </c>
+      <c r="C229" t="s">
+        <v>20</v>
+      </c>
+      <c r="F229">
+        <v>2779411084</v>
+      </c>
+      <c r="G229" s="2">
+        <v>1790951523271790</v>
+      </c>
+      <c r="H229" t="s">
+        <v>21</v>
+      </c>
+      <c r="I229" t="s">
+        <v>32</v>
+      </c>
+      <c r="J229" t="s">
+        <v>23</v>
+      </c>
+      <c r="K229" t="s">
+        <v>37</v>
+      </c>
+      <c r="N229" t="s">
+        <v>29</v>
+      </c>
+      <c r="O229">
+        <v>19</v>
+      </c>
+      <c r="R229" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S229" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="230" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A230" s="1">
+        <v>46297.482789351852</v>
+      </c>
+      <c r="B230" t="s">
+        <v>19</v>
+      </c>
+      <c r="C230" t="s">
+        <v>20</v>
+      </c>
+      <c r="F230">
+        <v>2763039330</v>
+      </c>
+      <c r="G230" s="2">
+        <v>1790951713278260</v>
+      </c>
+      <c r="H230" t="s">
+        <v>21</v>
+      </c>
+      <c r="I230" t="s">
+        <v>77</v>
+      </c>
+      <c r="J230" t="s">
+        <v>23</v>
+      </c>
+      <c r="K230" t="s">
+        <v>24</v>
+      </c>
+      <c r="L230" t="s">
+        <v>35</v>
+      </c>
+      <c r="N230" t="s">
+        <v>25</v>
+      </c>
+      <c r="O230">
+        <v>16</v>
+      </c>
+      <c r="R230" s="3">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="S230" s="3">
+        <v>8.1018518518518516E-4</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:S230" xr:uid="{100F3FCB-6525-4D20-BE0A-5478D5F6F3FE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>